--- a/results/six_week_reports_20261028/report_01_CN距離容差與Solver.xlsx
+++ b/results/six_week_reports_20261028/report_01_CN距離容差與Solver.xlsx
@@ -9,11 +9,14 @@
   <sheets>
     <sheet name="四組結果比較" sheetId="1" r:id="rId1"/>
     <sheet name="設定與說明" sheetId="2" r:id="rId2"/>
+    <sheet name="精度時間與成對比較" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">四組結果比較!$A$1:$H$45</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">設定與說明!$A$1:$H$29</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">四組結果比較!$A$1:$H$73</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">精度時間與成對比較!$A$1:$H$52</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">設定與說明!$A$1:$H$46</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">四組結果比較!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">精度時間與成對比較!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">設定與說明!$1:$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="118">
   <si>
     <t>第1次｜CN距離容差與Solver</t>
   </si>
@@ -32,169 +35,260 @@
     <t>GT不參與當次配準輸出選擇；開發期間曾以GT評分選設定。相同掃描站換seed只測隨機敏感度，不是未見森林。</t>
   </si>
   <si>
-    <t>只改CN距離容差與Solver；四組補救均關閉</t>
-  </si>
-  <si>
-    <t>CN／Solver</t>
+    <t>兩組dataset；每個場景都比較相同四組，補救全部關閉</t>
+  </si>
+  <si>
+    <t>dataset／場景</t>
+  </si>
+  <si>
+    <t>案例組成</t>
+  </si>
+  <si>
+    <t>5cm／SVD</t>
+  </si>
+  <si>
+    <t>5cm／RANSAC</t>
+  </si>
+  <si>
+    <t>10cm／SVD</t>
+  </si>
+  <si>
+    <t>10cm／RANSAC</t>
+  </si>
+  <si>
+    <t>論文成功率
+分母待補</t>
+  </si>
+  <si>
+    <t>論文e_p cm</t>
+  </si>
+  <si>
+    <t>Tongji／Plot1</t>
+  </si>
+  <si>
+    <t>10配對×10seed</t>
+  </si>
+  <si>
+    <t>Tongji／Plot2</t>
+  </si>
+  <si>
+    <t>Tongji／Plot3</t>
+  </si>
+  <si>
+    <t>Tongji／Plot4</t>
+  </si>
+  <si>
+    <t>ETH-tree</t>
+  </si>
+  <si>
+    <t>15配對×10seed</t>
+  </si>
+  <si>
+    <t>統一seed31–40：Tongji每Plot五站、10對×10seed；ETH六站、15對×10seed。ETH四組為本次補跑，先前118/123/135/142屬seed11–20，保留為歷史資料。Tongji四Plot是同一dataset。</t>
+  </si>
+  <si>
+    <t>有限mean e_p（cm），包含可計算失敗；樣本數另列</t>
+  </si>
+  <si>
+    <t>有限誤差樣本數：缺變換是失敗，e_p不填0</t>
+  </si>
+  <si>
+    <t>ETH改善不能直接外推Tongji。Plot2部分改善、Plot4退步；有限案例集合不同時不直接算誤差下降率。完整e_R/e_t、時間及共同成功見第三頁。</t>
+  </si>
+  <si>
+    <t>本週只看兩個變數</t>
+  </si>
+  <si>
+    <t>項目</t>
+  </si>
+  <si>
+    <t>前／設定A</t>
+  </si>
+  <si>
+    <t>後／設定B</t>
+  </si>
+  <si>
+    <t>作用與固定條件</t>
+  </si>
+  <si>
+    <t>CN距離容差</t>
+  </si>
+  <si>
+    <t>0.05m</t>
+  </si>
+  <si>
+    <t>0.10m</t>
+  </si>
+  <si>
+    <t>允許descriptor距離差更大；也可能增加錯配</t>
+  </si>
+  <si>
+    <t>Solver</t>
+  </si>
+  <si>
+    <t>Kabsch／SVD</t>
+  </si>
+  <si>
+    <t>Kabsch＋RANSAC</t>
+  </si>
+  <si>
+    <t>先尋找3D一致群，再估剛體變換</t>
+  </si>
+  <si>
+    <t>弱配對補救</t>
+  </si>
+  <si>
+    <t>關閉</t>
+  </si>
+  <si>
+    <t>第一週固定，不介紹或歸因此模組</t>
+  </si>
+  <si>
+    <t>提取與descriptor</t>
+  </si>
+  <si>
+    <t>同一批樹位</t>
+  </si>
+  <si>
+    <t>同前</t>
+  </si>
+  <si>
+    <t>step、分群0.20m、verticality&gt;0.9；N183/w10/Thscore40固定</t>
+  </si>
+  <si>
+    <t>固定另一項，逐場景看單項改動</t>
+  </si>
+  <si>
+    <t>場景</t>
+  </si>
+  <si>
+    <t>固定條件</t>
+  </si>
+  <si>
+    <t>唯一改動</t>
+  </si>
+  <si>
+    <t>前成功數</t>
+  </si>
+  <si>
+    <t>後成功數</t>
+  </si>
+  <si>
+    <t>後−前 pp</t>
+  </si>
+  <si>
+    <t>成功數淨增加</t>
+  </si>
+  <si>
+    <t>比較限制</t>
+  </si>
+  <si>
+    <t>SVD固定</t>
+  </si>
+  <si>
+    <t>5→10cm</t>
+  </si>
+  <si>
+    <t>100/100</t>
+  </si>
+  <si>
+    <t>待補</t>
+  </si>
+  <si>
+    <t>只在同場景、同seed內比較</t>
+  </si>
+  <si>
+    <t>RANSAC固定</t>
+  </si>
+  <si>
+    <t>5cm固定</t>
+  </si>
+  <si>
+    <t>SVD→RANSAC</t>
+  </si>
+  <si>
+    <t>10cm固定</t>
+  </si>
+  <si>
+    <t>33/100</t>
+  </si>
+  <si>
+    <t>37/100</t>
+  </si>
+  <si>
+    <t>28/100</t>
+  </si>
+  <si>
+    <t>34/100</t>
+  </si>
+  <si>
+    <t>76/100</t>
+  </si>
+  <si>
+    <t>69/100</t>
+  </si>
+  <si>
+    <t>70/100</t>
+  </si>
+  <si>
+    <t>114/150</t>
+  </si>
+  <si>
+    <t>138/150</t>
+  </si>
+  <si>
+    <t>121/150</t>
+  </si>
+  <si>
+    <t>144/150</t>
+  </si>
+  <si>
+    <t>RANSAC固定設定為最多1000次抽樣嘗試、3D inlier&lt;0.30m、seed1；它們是solver定義，這週沒有各常數消融。GT正確matching欄只檢查XY&lt;0.30m，因此XY正確也可能存在z不一致。</t>
+  </si>
+  <si>
+    <t>時間為descriptor＋matching＋solver，不含樹位提取、原始點雲讀取及GT誤差評估。舊批次OpenMP4，CPU型號與並行干擾未完整控制，只作本批描述性代價；不能與論文matching／total時間直接算速度提升。</t>
+  </si>
+  <si>
+    <t>論文TableI的ETH e_p=15.3427cm，Tongji Plot1～4=5.2558/11.4808/4.8756/4.3560cm，各報100%；分母與成功門檻待補。四組本地控制實驗不是作者程式重跑；目前結果不支持「這兩項改動在所有場景都改善」。</t>
+  </si>
+  <si>
+    <t>數據來源與比較限制</t>
+  </si>
+  <si>
+    <t>F：results/six_week_reports_20261028/evidence/F_eth_coarse_rows.csv；SHA256 7d650dccaae06db5a5425d39e9b7844210caaca64422f3b7240e5adb18e8a876</t>
+  </si>
+  <si>
+    <t>T：results/six_week_reports_20261028/evidence/T_registration_rows.csv；SHA256 be80ea133faf080bae060279ab9401346bb3263f319589450ec998822f1913a1</t>
+  </si>
+  <si>
+    <t>論文：Sun等，DOI 10.1109/LGRS.2025.3650098。PDF p2方法、p3 Algorithm1、p4 TableI/II與Eq8、p5 TableIII。作者程式同環境重跑、論文成功門檻與逐場景分母待補；本地5cm參考不是作者可執行baseline。</t>
+  </si>
+  <si>
+    <t>四組×五場景：精度與時間，未混算兩來源平均</t>
+  </si>
+  <si>
+    <t>組合</t>
+  </si>
+  <si>
+    <t>finite mean e_p cm</t>
+  </si>
+  <si>
+    <t>有限N</t>
+  </si>
+  <si>
+    <t>mean e_R °</t>
+  </si>
+  <si>
+    <t>mean e_t cm</t>
+  </si>
+  <si>
+    <t>平均time_ms</t>
   </si>
   <si>
     <t>成功／總數</t>
   </si>
   <si>
-    <t>成功率</t>
-  </si>
-  <si>
-    <t>有限mean e_p cm</t>
-  </si>
-  <si>
-    <t>有限N</t>
-  </si>
-  <si>
-    <t>mean e_R °</t>
-  </si>
-  <si>
-    <t>mean e_t cm</t>
-  </si>
-  <si>
-    <t>平均time_ms</t>
-  </si>
-  <si>
-    <t>5cm／SVD</t>
-  </si>
-  <si>
-    <t>118/150</t>
-  </si>
-  <si>
-    <t>5cm／RANSAC</t>
-  </si>
-  <si>
-    <t>123/150</t>
-  </si>
-  <si>
-    <t>10cm／SVD</t>
-  </si>
-  <si>
-    <t>135/150</t>
-  </si>
-  <si>
-    <t>10cm／RANSAC</t>
-  </si>
-  <si>
-    <t>142/150</t>
-  </si>
-  <si>
-    <t>ETH-tree六站、15個固定兩站配對×seed11–20，各150次；四組使用相同提取樹位。有限N為130／130／143／143，故5→10cm的有限mean不直接計下降率。e_R/e_t亦僅平均可計算值。</t>
-  </si>
-  <si>
-    <t>一次只改一項：讀懂四組組合</t>
-  </si>
-  <si>
-    <t>固定條件</t>
-  </si>
-  <si>
-    <t>唯一改動</t>
-  </si>
-  <si>
-    <t>前成功數</t>
-  </si>
-  <si>
-    <t>後成功數</t>
-  </si>
-  <si>
-    <t>前成功率</t>
-  </si>
-  <si>
-    <t>後成功率</t>
-  </si>
-  <si>
-    <t>差：後−前 pp</t>
-  </si>
-  <si>
-    <t>成功數淨增加</t>
-  </si>
-  <si>
-    <t>SVD固定</t>
-  </si>
-  <si>
-    <t>5→10cm</t>
-  </si>
-  <si>
-    <t>待補</t>
-  </si>
-  <si>
-    <t>RANSAC固定</t>
-  </si>
-  <si>
-    <t>5cm固定</t>
-  </si>
-  <si>
-    <t>SVD→RANSAC</t>
-  </si>
-  <si>
-    <t>10cm固定</t>
-  </si>
-  <si>
-    <t>成功數淨增加不是「新增成功且完全無退步」；精確新增／退步與共同成功比較見第二頁。整體5cm/SVD→10cm/RANSAC為118→142，但不可把24次全歸給單一變數。</t>
-  </si>
-  <si>
-    <t>本週只看兩個變數</t>
-  </si>
-  <si>
-    <t>項目</t>
-  </si>
-  <si>
-    <t>前／設定A</t>
-  </si>
-  <si>
-    <t>後／設定B</t>
-  </si>
-  <si>
-    <t>作用與固定條件</t>
-  </si>
-  <si>
-    <t>CN距離容差</t>
-  </si>
-  <si>
-    <t>0.05m</t>
-  </si>
-  <si>
-    <t>0.10m</t>
-  </si>
-  <si>
-    <t>允許descriptor距離差更大；也可能增加錯配</t>
-  </si>
-  <si>
-    <t>Solver</t>
-  </si>
-  <si>
-    <t>Kabsch／SVD</t>
-  </si>
-  <si>
-    <t>Kabsch＋RANSAC</t>
-  </si>
-  <si>
-    <t>先尋找3D一致群，再估剛體變換</t>
-  </si>
-  <si>
-    <t>弱配對補救</t>
-  </si>
-  <si>
-    <t>關閉</t>
-  </si>
-  <si>
-    <t>第一週固定，不介紹或歸因此模組</t>
-  </si>
-  <si>
-    <t>提取與descriptor</t>
-  </si>
-  <si>
-    <t>同一批樹位</t>
-  </si>
-  <si>
-    <t>同前</t>
-  </si>
-  <si>
-    <t>step、分群0.20m、verticality&gt;0.9；N183/w10/Thscore40固定</t>
+    <t>e_R/e_t亦平均可計算值、包含有限失敗。time_ms只含descriptor＋matching＋solver；不同來源批次不作跨dataset速度排名。沒有變換的案例仍算成功率失敗。</t>
   </si>
   <si>
     <t>相同配對與seed：新增成功、退步與共同成功精度</t>
@@ -224,47 +318,89 @@
     <t>限制</t>
   </si>
   <si>
-    <t>SVD固定：5→10cm</t>
+    <t>Tongji／Plot1；SVD固定；5→10cm</t>
   </si>
   <si>
     <t>僅共同成功；不取代全體成功率</t>
   </si>
   <si>
-    <t>RANSAC固定：5→10cm</t>
-  </si>
-  <si>
-    <t>5cm固定：SVD→RANSAC</t>
-  </si>
-  <si>
-    <t>10cm固定：SVD→RANSAC</t>
-  </si>
-  <si>
-    <t>RANSAC固定設定為最多1000次抽樣嘗試、3D inlier&lt;0.30m、seed1；它們是solver定義，這週沒有各常數消融。GT正確matching欄只檢查XY&lt;0.30m，因此XY正確也可能存在z不一致。</t>
-  </si>
-  <si>
-    <t>時間為descriptor＋matching＋solver，不含樹位提取、原始點雲讀取及GT誤差評估。舊批次OpenMP4，CPU型號與並行干擾未完整控制，只作本批描述性代價；不能與論文matching／total時間直接算速度提升。</t>
-  </si>
-  <si>
-    <t>論文TableI的ETH e_p=15.3427cm、成功率100%，分母與成功門檻待補。四組本地結果是控制實驗，不是原作者程式重跑；本週尚不宣稱跨Tongji有效或嚴格超越原作。</t>
-  </si>
-  <si>
-    <t>數據來源與比較限制</t>
-  </si>
-  <si>
-    <t>F：results/professor_reports_20261026/evidence/F_fresh_rows.csv；SHA256 b73cafe4af6c29e65881e8fa481474ab1c304aaa273ba2c7185fbddbf90098bb</t>
-  </si>
-  <si>
-    <t>論文：Sun等，DOI 10.1109/LGRS.2025.3650098。PDF p2方法、p3 Algorithm1、p4 TableI/II與Eq8、p5 TableIII。作者程式同環境重跑、論文成功門檻與逐場景分母待補；本地5cm參考不是作者可執行baseline。</t>
+    <t>Tongji／Plot1；RANSAC固定；5→10cm</t>
+  </si>
+  <si>
+    <t>Tongji／Plot1；5cm固定；SVD→RANSAC</t>
+  </si>
+  <si>
+    <t>Tongji／Plot1；10cm固定；SVD→RANSAC</t>
+  </si>
+  <si>
+    <t>Tongji／Plot2；SVD固定；5→10cm</t>
+  </si>
+  <si>
+    <t>Tongji／Plot2；RANSAC固定；5→10cm</t>
+  </si>
+  <si>
+    <t>Tongji／Plot2；5cm固定；SVD→RANSAC</t>
+  </si>
+  <si>
+    <t>Tongji／Plot2；10cm固定；SVD→RANSAC</t>
+  </si>
+  <si>
+    <t>Tongji／Plot3；SVD固定；5→10cm</t>
+  </si>
+  <si>
+    <t>Tongji／Plot3；RANSAC固定；5→10cm</t>
+  </si>
+  <si>
+    <t>Tongji／Plot3；5cm固定；SVD→RANSAC</t>
+  </si>
+  <si>
+    <t>Tongji／Plot3；10cm固定；SVD→RANSAC</t>
+  </si>
+  <si>
+    <t>Tongji／Plot4；SVD固定；5→10cm</t>
+  </si>
+  <si>
+    <t>Tongji／Plot4；RANSAC固定；5→10cm</t>
+  </si>
+  <si>
+    <t>Tongji／Plot4；5cm固定；SVD→RANSAC</t>
+  </si>
+  <si>
+    <t>Tongji／Plot4；10cm固定；SVD→RANSAC</t>
+  </si>
+  <si>
+    <t>ETH-tree；SVD固定；5→10cm</t>
+  </si>
+  <si>
+    <t>ETH-tree；RANSAC固定；5→10cm</t>
+  </si>
+  <si>
+    <t>ETH-tree；5cm固定；SVD→RANSAC</t>
+  </si>
+  <si>
+    <t>ETH-tree；10cm固定；SVD→RANSAC</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
-    <numFmt numFmtId="166" formatCode="0.0&quot; pp&quot;"/>
+  <numFmts count="15">
+    <numFmt numFmtId="164" formatCode="&quot;100/100 (&quot;0.0%&quot;)&quot;"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="&quot;33/100 (&quot;0.0%&quot;)&quot;"/>
+    <numFmt numFmtId="168" formatCode="&quot;28/100 (&quot;0.0%&quot;)&quot;"/>
+    <numFmt numFmtId="169" formatCode="&quot;37/100 (&quot;0.0%&quot;)&quot;"/>
+    <numFmt numFmtId="170" formatCode="&quot;34/100 (&quot;0.0%&quot;)&quot;"/>
+    <numFmt numFmtId="171" formatCode="&quot;76/100 (&quot;0.0%&quot;)&quot;"/>
+    <numFmt numFmtId="172" formatCode="&quot;69/100 (&quot;0.0%&quot;)&quot;"/>
+    <numFmt numFmtId="173" formatCode="&quot;70/100 (&quot;0.0%&quot;)&quot;"/>
+    <numFmt numFmtId="174" formatCode="&quot;114/150 (&quot;0.0%&quot;)&quot;"/>
+    <numFmt numFmtId="175" formatCode="&quot;121/150 (&quot;0.0%&quot;)&quot;"/>
+    <numFmt numFmtId="176" formatCode="&quot;138/150 (&quot;0.0%&quot;)&quot;"/>
+    <numFmt numFmtId="177" formatCode="&quot;144/150 (&quot;0.0%&quot;)&quot;"/>
+    <numFmt numFmtId="178" formatCode="0.0&quot; pp&quot;"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -327,7 +463,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -342,15 +478,48 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="174" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="175" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -377,7 +546,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>四組成功率</a:t>
+              <a:t>四組成功率：各場景分開</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -398,14 +567,14 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>成功率</c:v>
+                  <c:v>5cm／SVD</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="7E8D98"/>
+              <a:srgbClr val="9BA7B0"/>
             </a:solidFill>
           </c:spPr>
           <c:dLbls>
@@ -414,41 +583,260 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>四組結果比較!$A$7:$A$10</c:f>
+              <c:f>四組結果比較!$A$7:$A$11</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>5cm／SVD</c:v>
+                  <c:v>Tongji／Plot1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5cm／RANSAC</c:v>
+                  <c:v>Tongji／Plot2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>10cm／SVD</c:v>
+                  <c:v>Tongji／Plot3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>10cm／RANSAC</c:v>
+                  <c:v>Tongji／Plot4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>ETH-tree</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>四組結果比較!$C$7:$C$10</c:f>
+              <c:f>四組結果比較!$C$7:$C$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>0.7866666666666666</c:v>
+                  <c:v>1.0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.82</c:v>
+                  <c:v>0.33</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.9</c:v>
+                  <c:v>1.0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.9466666666666667</c:v>
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.76</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>四組結果比較!$D$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>5cm／RANSAC</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="5B7790"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>四組結果比較!$A$7:$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Tongji／Plot1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Tongji／Plot2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Tongji／Plot3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Tongji／Plot4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>ETH-tree</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>四組結果比較!$D$7:$D$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.28</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.8066666666666666</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>四組結果比較!$E$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>10cm／SVD</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="708FA3"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>四組結果比較!$A$7:$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Tongji／Plot1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Tongji／Plot2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Tongji／Plot3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Tongji／Plot4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>ETH-tree</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>四組結果比較!$E$7:$E$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.37</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.69</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.92</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>四組結果比較!$F$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>10cm／RANSAC</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="254E70"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>四組結果比較!$A$7:$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Tongji／Plot1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Tongji／Plot2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Tongji／Plot3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Tongji／Plot4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>ETH-tree</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>四組結果比較!$F$7:$F$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.34</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.96</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -504,6 +892,10 @@
         <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+    </c:legend>
     <c:plotVisOnly val="1"/>
   </c:chart>
   <c:printSettings>
@@ -546,18 +938,18 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>四組結果比較!$D$6</c:f>
+              <c:f>四組結果比較!$B$17</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>有限mean e_p cm</c:v>
+                  <c:v>5cm／SVD</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="7E8D98"/>
+              <a:srgbClr val="9BA7B0"/>
             </a:solidFill>
           </c:spPr>
           <c:dLbls>
@@ -566,41 +958,260 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>四組結果比較!$A$7:$A$10</c:f>
+              <c:f>四組結果比較!$A$18:$A$22</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>5cm／SVD</c:v>
+                  <c:v>Tongji／Plot1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5cm／RANSAC</c:v>
+                  <c:v>Tongji／Plot2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>10cm／SVD</c:v>
+                  <c:v>Tongji／Plot3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>10cm／RANSAC</c:v>
+                  <c:v>Tongji／Plot4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>ETH-tree</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>四組結果比較!$D$7:$D$10</c:f>
+              <c:f>四組結果比較!$B$18:$B$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>15.01120221933077</c:v>
+                  <c:v>16.81264811113</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>15.06397582643077</c:v>
+                  <c:v>54.50497163930999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>11.22310207536364</c:v>
+                  <c:v>5.376450884124</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>9.774054196055944</c:v>
+                  <c:v>123.2346789297831</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>12.62093021071654</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>四組結果比較!$C$17</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>5cm／RANSAC</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="5B7790"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>四組結果比較!$A$18:$A$22</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Tongji／Plot1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Tongji／Plot2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Tongji／Plot3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Tongji／Plot4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>ETH-tree</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>四組結果比較!$C$18:$C$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>17.2083674392</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>58.201283144</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.291779501674</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>123.2346789297831</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10.97050868271654</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>四組結果比較!$D$17</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>10cm／SVD</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="708FA3"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>四組結果比較!$A$18:$A$22</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Tongji／Plot1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Tongji／Plot2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Tongji／Plot3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Tongji／Plot4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>ETH-tree</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>四組結果比較!$D$18:$D$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>17.66683273383</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>47.25469538884</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.993702343056</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>299.4917599032963</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10.72940896452414</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>四組結果比較!$E$17</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>10cm／RANSAC</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="254E70"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>四組結果比較!$A$18:$A$22</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Tongji／Plot1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Tongji／Plot2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Tongji／Plot3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Tongji／Plot4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>ETH-tree</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>四組結果比較!$E$18:$E$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>17.4235311056</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>50.90068114483</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.901756139286</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>252.1680517323086</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.095719413689656</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -655,6 +1266,10 @@
         <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+    </c:legend>
     <c:plotVisOnly val="1"/>
   </c:chart>
   <c:printSettings>
@@ -671,14 +1286,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>752475</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -699,15 +1314,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
+      <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1419225</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>752475</xdr:colOff>
+      <xdr:row>67</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -1018,7 +1633,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="27.7109375" customWidth="1"/>
@@ -1111,22 +1726,26 @@
         <v>13</v>
       </c>
       <c r="C7" s="5">
-        <v>0.7866666666666666</v>
-      </c>
-      <c r="D7" s="6">
-        <v>15.01120221933077</v>
-      </c>
-      <c r="E7" s="7">
-        <v>130</v>
-      </c>
-      <c r="F7" s="6">
-        <v>0.8333489008797692</v>
+        <f>100/100</f>
+        <v>1.0</v>
+      </c>
+      <c r="D7" s="5">
+        <f>100/100</f>
+        <v>1.0</v>
+      </c>
+      <c r="E7" s="5">
+        <f>100/100</f>
+        <v>1.0</v>
+      </c>
+      <c r="F7" s="5">
+        <f>100/100</f>
+        <v>1.0</v>
       </c>
       <c r="G7" s="6">
-        <v>13.54911137796461</v>
-      </c>
-      <c r="H7" s="6">
-        <v>4.097461013333334</v>
+        <v>1</v>
+      </c>
+      <c r="H7" s="7">
+        <v>5.2558</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="45" customHeight="1">
@@ -1134,258 +1753,401 @@
         <v>14</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="5">
-        <v>0.82</v>
-      </c>
-      <c r="D8" s="6">
-        <v>15.06397582643077</v>
-      </c>
-      <c r="E8" s="7">
-        <v>130</v>
-      </c>
-      <c r="F8" s="6">
-        <v>0.8415891027882307</v>
+        <v>13</v>
+      </c>
+      <c r="C8" s="8">
+        <f>33/100</f>
+        <v>0.33</v>
+      </c>
+      <c r="D8" s="9">
+        <f>28/100</f>
+        <v>0.28</v>
+      </c>
+      <c r="E8" s="10">
+        <f>37/100</f>
+        <v>0.37</v>
+      </c>
+      <c r="F8" s="11">
+        <f>34/100</f>
+        <v>0.34</v>
       </c>
       <c r="G8" s="6">
-        <v>13.67159712948</v>
-      </c>
-      <c r="H8" s="6">
-        <v>5.245315986666666</v>
+        <v>1</v>
+      </c>
+      <c r="H8" s="7">
+        <v>11.4808</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="45" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C9" s="5">
-        <v>0.9</v>
-      </c>
-      <c r="D9" s="6">
-        <v>11.22310207536364</v>
-      </c>
-      <c r="E9" s="7">
-        <v>143</v>
-      </c>
-      <c r="F9" s="6">
-        <v>0.7024714967154545</v>
+        <f>100/100</f>
+        <v>1.0</v>
+      </c>
+      <c r="D9" s="5">
+        <f>100/100</f>
+        <v>1.0</v>
+      </c>
+      <c r="E9" s="5">
+        <f>100/100</f>
+        <v>1.0</v>
+      </c>
+      <c r="F9" s="5">
+        <f>100/100</f>
+        <v>1.0</v>
       </c>
       <c r="G9" s="6">
-        <v>9.952239008971327</v>
-      </c>
-      <c r="H9" s="6">
-        <v>5.115265313333333</v>
+        <v>1</v>
+      </c>
+      <c r="H9" s="7">
+        <v>4.8756</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="45" customHeight="1">
       <c r="A10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="12">
+        <f>76/100</f>
+        <v>0.76</v>
+      </c>
+      <c r="D10" s="12">
+        <f>76/100</f>
+        <v>0.76</v>
+      </c>
+      <c r="E10" s="13">
+        <f>69/100</f>
+        <v>0.69</v>
+      </c>
+      <c r="F10" s="14">
+        <f>70/100</f>
+        <v>0.7</v>
+      </c>
+      <c r="G10" s="6">
+        <v>1</v>
+      </c>
+      <c r="H10" s="7">
+        <v>4.356</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="45" customHeight="1">
+      <c r="A11" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="C11" s="15">
+        <f>114/150</f>
+        <v>0.76</v>
+      </c>
+      <c r="D11" s="16">
+        <f>121/150</f>
+        <v>0.8066666666666666</v>
+      </c>
+      <c r="E11" s="17">
+        <f>138/150</f>
+        <v>0.92</v>
+      </c>
+      <c r="F11" s="18">
+        <f>144/150</f>
+        <v>0.96</v>
+      </c>
+      <c r="G11" s="6">
+        <v>1</v>
+      </c>
+      <c r="H11" s="7">
+        <v>15.3427</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="48" customHeight="1">
+      <c r="A14" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="5">
-        <v>0.9466666666666667</v>
-      </c>
-      <c r="D10" s="6">
-        <v>9.774054196055944</v>
-      </c>
-      <c r="E10" s="7">
-        <v>143</v>
-      </c>
-      <c r="F10" s="6">
-        <v>0.558572264859021</v>
-      </c>
-      <c r="G10" s="6">
-        <v>8.81331026267063</v>
-      </c>
-      <c r="H10" s="6">
-        <v>6.842217106666666</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="46" customHeight="1">
-      <c r="A13" s="2" t="s">
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+    </row>
+    <row r="16" spans="1:8" ht="28" customHeight="1">
+      <c r="A16" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-    </row>
-    <row r="15" spans="1:8" ht="28" customHeight="1">
-      <c r="A15" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-    </row>
-    <row r="16" spans="1:8" ht="40" customHeight="1">
-      <c r="A16" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="45" customHeight="1">
-      <c r="A17" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E17" s="5">
-        <v>0.7866666666666666</v>
-      </c>
-      <c r="F17" s="5">
-        <v>0.9</v>
-      </c>
-      <c r="G17" s="8">
-        <f>(F17-E17)*100</f>
-        <v>11.33333333333334</v>
-      </c>
-      <c r="H17" s="7">
-        <v>17</v>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+    </row>
+    <row r="17" spans="1:8" ht="40" customHeight="1">
+      <c r="A17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="45" customHeight="1">
       <c r="A18" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E18" s="5">
-        <v>0.82</v>
-      </c>
-      <c r="F18" s="5">
-        <v>0.9466666666666667</v>
-      </c>
-      <c r="G18" s="8">
-        <f>(F18-E18)*100</f>
-        <v>12.666666666666671</v>
-      </c>
-      <c r="H18" s="7">
-        <v>19</v>
+        <v>12</v>
+      </c>
+      <c r="B18" s="7">
+        <v>16.81264811113</v>
+      </c>
+      <c r="C18" s="7">
+        <v>17.2083674392</v>
+      </c>
+      <c r="D18" s="7">
+        <v>17.66683273383</v>
+      </c>
+      <c r="E18" s="7">
+        <v>17.4235311056</v>
+      </c>
+      <c r="F18" s="7">
+        <v>5.2558</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="45" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E19" s="5">
-        <v>0.7866666666666666</v>
-      </c>
-      <c r="F19" s="5">
-        <v>0.82</v>
-      </c>
-      <c r="G19" s="8">
-        <f>(F19-E19)*100</f>
-        <v>3.3333333333333326</v>
-      </c>
-      <c r="H19" s="7">
-        <v>5</v>
+        <v>14</v>
+      </c>
+      <c r="B19" s="7">
+        <v>54.50497163930999</v>
+      </c>
+      <c r="C19" s="7">
+        <v>58.201283144</v>
+      </c>
+      <c r="D19" s="7">
+        <v>47.25469538884</v>
+      </c>
+      <c r="E19" s="7">
+        <v>50.90068114483</v>
+      </c>
+      <c r="F19" s="7">
+        <v>11.4808</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="45" customHeight="1">
       <c r="A20" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C20" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="7">
+        <v>5.376450884124</v>
+      </c>
+      <c r="C20" s="7">
+        <v>5.291779501674</v>
+      </c>
+      <c r="D20" s="7">
+        <v>4.993702343056</v>
+      </c>
+      <c r="E20" s="7">
+        <v>4.901756139286</v>
+      </c>
+      <c r="F20" s="7">
+        <v>4.8756</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="45" customHeight="1">
+      <c r="A21" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" s="7">
+        <v>123.2346789297831</v>
+      </c>
+      <c r="C21" s="7">
+        <v>123.2346789297831</v>
+      </c>
+      <c r="D21" s="7">
+        <v>299.4917599032963</v>
+      </c>
+      <c r="E21" s="7">
+        <v>252.1680517323086</v>
+      </c>
+      <c r="F21" s="7">
+        <v>4.356</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="45" customHeight="1">
+      <c r="A22" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D20" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E20" s="5">
-        <v>0.9</v>
-      </c>
-      <c r="F20" s="5">
-        <v>0.9466666666666667</v>
-      </c>
-      <c r="G20" s="8">
-        <f>(F20-E20)*100</f>
-        <v>4.666666666666663</v>
-      </c>
-      <c r="H20" s="7">
+      <c r="B22" s="7">
+        <v>12.62093021071654</v>
+      </c>
+      <c r="C22" s="7">
+        <v>10.97050868271654</v>
+      </c>
+      <c r="D22" s="7">
+        <v>10.72940896452414</v>
+      </c>
+      <c r="E22" s="7">
+        <v>9.095719413689656</v>
+      </c>
+      <c r="F22" s="7">
+        <v>15.3427</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="28" customHeight="1">
+      <c r="A25" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+    </row>
+    <row r="26" spans="1:8" ht="40" customHeight="1">
+      <c r="A26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" ht="44" customHeight="1">
-      <c r="A23" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
+      <c r="D26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="45" customHeight="1">
+      <c r="A27" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B27" s="4">
+        <v>100</v>
+      </c>
+      <c r="C27" s="4">
+        <v>100</v>
+      </c>
+      <c r="D27" s="4">
+        <v>100</v>
+      </c>
+      <c r="E27" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="45" customHeight="1">
+      <c r="A28" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" s="4">
+        <v>100</v>
+      </c>
+      <c r="C28" s="4">
+        <v>100</v>
+      </c>
+      <c r="D28" s="4">
+        <v>100</v>
+      </c>
+      <c r="E28" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="45" customHeight="1">
+      <c r="A29" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" s="4">
+        <v>100</v>
+      </c>
+      <c r="C29" s="4">
+        <v>100</v>
+      </c>
+      <c r="D29" s="4">
+        <v>100</v>
+      </c>
+      <c r="E29" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="45" customHeight="1">
+      <c r="A30" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B30" s="4">
+        <v>83</v>
+      </c>
+      <c r="C30" s="4">
+        <v>83</v>
+      </c>
+      <c r="D30" s="4">
+        <v>81</v>
+      </c>
+      <c r="E30" s="4">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="45" customHeight="1">
+      <c r="A31" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B31" s="4">
+        <v>127</v>
+      </c>
+      <c r="C31" s="4">
+        <v>127</v>
+      </c>
+      <c r="D31" s="4">
+        <v>145</v>
+      </c>
+      <c r="E31" s="4">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="42" customHeight="1">
+      <c r="A34" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A34:H34"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.4" bottom="0.4" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" fitToHeight="0" orientation="landscape"/>
@@ -1402,7 +2164,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="27.7109375" customWidth="1"/>
@@ -1451,7 +2213,7 @@
     </row>
     <row r="5" spans="1:8" ht="28" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -1463,77 +2225,77 @@
     </row>
     <row r="6" spans="1:8" ht="40" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="45" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="45" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="45" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="45" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="28" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -1545,201 +2307,1291 @@
     </row>
     <row r="14" spans="1:8" ht="40" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="45" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B15" s="4">
-        <v>25</v>
-      </c>
-      <c r="C15" s="4">
-        <v>8</v>
-      </c>
-      <c r="D15" s="4">
-        <v>110</v>
-      </c>
-      <c r="E15" s="6">
-        <v>9.236036107445454</v>
-      </c>
-      <c r="F15" s="6">
-        <v>9.154550424772728</v>
-      </c>
-      <c r="G15" s="5">
-        <f>IF(AND(ISNUMBER(E15),ISNUMBER(F15),E15&lt;&gt;0),(E15-F15)/E15,"待補")</f>
-        <v>0.008822581649181637</v>
+        <v>12</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F15" s="19">
+        <f>(100/100-100/100)*100</f>
+        <v>0.0</v>
+      </c>
+      <c r="G15" s="4">
+        <v>0</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="45" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B16" s="4">
-        <v>26</v>
-      </c>
-      <c r="C16" s="4">
-        <v>7</v>
-      </c>
-      <c r="D16" s="4">
-        <v>116</v>
-      </c>
-      <c r="E16" s="6">
-        <v>9.375305286482758</v>
-      </c>
-      <c r="F16" s="6">
-        <v>8.491122205905171</v>
-      </c>
-      <c r="G16" s="5">
-        <f>IF(AND(ISNUMBER(E16),ISNUMBER(F16),E16&lt;&gt;0),(E16-F16)/E16,"待補")</f>
-        <v>0.09430979083448038</v>
+        <v>12</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F16" s="19">
+        <f>(100/100-100/100)*100</f>
+        <v>0.0</v>
+      </c>
+      <c r="G16" s="4">
+        <v>0</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="45" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B17" s="4">
-        <v>5</v>
-      </c>
-      <c r="C17" s="4">
+        <v>12</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F17" s="19">
+        <f>(100/100-100/100)*100</f>
+        <v>0.0</v>
+      </c>
+      <c r="G17" s="4">
         <v>0</v>
       </c>
-      <c r="D17" s="4">
-        <v>118</v>
-      </c>
-      <c r="E17" s="6">
-        <v>9.806986151381356</v>
-      </c>
-      <c r="F17" s="6">
-        <v>9.638276207067795</v>
-      </c>
-      <c r="G17" s="5">
-        <f>IF(AND(ISNUMBER(E17),ISNUMBER(F17),E17&lt;&gt;0),(E17-F17)/E17,"待補")</f>
-        <v>0.017203036866713227</v>
-      </c>
       <c r="H17" s="4" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="45" customHeight="1">
       <c r="A18" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F18" s="19">
+        <f>(100/100-100/100)*100</f>
+        <v>0.0</v>
+      </c>
+      <c r="G18" s="4">
+        <v>0</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="45" customHeight="1">
+      <c r="A19" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F19" s="19">
+        <f>(37/100-33/100)*100</f>
+        <v>3.9999999999999982</v>
+      </c>
+      <c r="G19" s="4">
+        <v>4</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="45" customHeight="1">
+      <c r="A20" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F20" s="19">
+        <f>(34/100-28/100)*100</f>
+        <v>6.0</v>
+      </c>
+      <c r="G20" s="4">
+        <v>6</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="45" customHeight="1">
+      <c r="A21" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F21" s="19">
+        <f>(28/100-33/100)*100</f>
+        <v>-4.999999999999999</v>
+      </c>
+      <c r="G21" s="4">
+        <v>-5</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="45" customHeight="1">
+      <c r="A22" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F22" s="19">
+        <f>(34/100-37/100)*100</f>
+        <v>-2.9999999999999973</v>
+      </c>
+      <c r="G22" s="4">
+        <v>-3</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="45" customHeight="1">
+      <c r="A23" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F23" s="19">
+        <f>(100/100-100/100)*100</f>
+        <v>0.0</v>
+      </c>
+      <c r="G23" s="4">
+        <v>0</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="45" customHeight="1">
+      <c r="A24" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F24" s="19">
+        <f>(100/100-100/100)*100</f>
+        <v>0.0</v>
+      </c>
+      <c r="G24" s="4">
+        <v>0</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="45" customHeight="1">
+      <c r="A25" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F25" s="19">
+        <f>(100/100-100/100)*100</f>
+        <v>0.0</v>
+      </c>
+      <c r="G25" s="4">
+        <v>0</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="45" customHeight="1">
+      <c r="A26" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F26" s="19">
+        <f>(100/100-100/100)*100</f>
+        <v>0.0</v>
+      </c>
+      <c r="G26" s="4">
+        <v>0</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="45" customHeight="1">
+      <c r="A27" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F27" s="19">
+        <f>(69/100-76/100)*100</f>
+        <v>-7.000000000000006</v>
+      </c>
+      <c r="G27" s="4">
+        <v>-7</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="45" customHeight="1">
+      <c r="A28" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F28" s="19">
+        <f>(70/100-76/100)*100</f>
+        <v>-6.000000000000005</v>
+      </c>
+      <c r="G28" s="4">
+        <v>-6</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="45" customHeight="1">
+      <c r="A29" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F29" s="19">
+        <f>(76/100-76/100)*100</f>
+        <v>0.0</v>
+      </c>
+      <c r="G29" s="4">
+        <v>0</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="45" customHeight="1">
+      <c r="A30" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F30" s="19">
+        <f>(70/100-69/100)*100</f>
+        <v>1.0000000000000009</v>
+      </c>
+      <c r="G30" s="4">
+        <v>1</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="45" customHeight="1">
+      <c r="A31" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F31" s="19">
+        <f>(138/150-114/150)*100</f>
+        <v>16.000000000000004</v>
+      </c>
+      <c r="G31" s="4">
+        <v>24</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="45" customHeight="1">
+      <c r="A32" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E32" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="B18" s="4">
+      <c r="F32" s="19">
+        <f>(144/150-121/150)*100</f>
+        <v>15.333333333333332</v>
+      </c>
+      <c r="G32" s="4">
+        <v>23</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="45" customHeight="1">
+      <c r="A33" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F33" s="19">
+        <f>(121/150-114/150)*100</f>
+        <v>4.666666666666663</v>
+      </c>
+      <c r="G33" s="4">
         <v>7</v>
       </c>
-      <c r="C18" s="4">
+      <c r="H33" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="45" customHeight="1">
+      <c r="A34" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="F34" s="19">
+        <f>(144/150-138/150)*100</f>
+        <v>3.9999999999999925</v>
+      </c>
+      <c r="G34" s="4">
+        <v>6</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="46" customHeight="1">
+      <c r="A37" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+    </row>
+    <row r="39" spans="1:8" ht="46" customHeight="1">
+      <c r="A39" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+    </row>
+    <row r="41" spans="1:8" ht="46" customHeight="1">
+      <c r="A41" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+    </row>
+    <row r="43" spans="1:8" ht="28" customHeight="1">
+      <c r="A43" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+      <c r="H43" s="3"/>
+    </row>
+    <row r="44" spans="1:8" ht="38" customHeight="1">
+      <c r="A44" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+    </row>
+    <row r="45" spans="1:8" ht="38" customHeight="1">
+      <c r="A45" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+    </row>
+    <row r="46" spans="1:8" ht="52" customHeight="1">
+      <c r="A46" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A39:H39"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="A43:H43"/>
+    <mergeCell ref="A44:H44"/>
+    <mergeCell ref="A45:H45"/>
+    <mergeCell ref="A46:H46"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.4" bottom="0.4" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="8" fitToHeight="0" orientation="landscape"/>
+  <headerFooter>
+    <oddHeader>&amp;C第1次｜CN距離容差與Solver</oddHeader>
+    <oddFooter>&amp;L單位依欄名；pp為百分點&amp;R&amp;P / &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H52"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="27.7109375" customWidth="1"/>
+    <col min="2" max="2" width="21.7109375" customWidth="1"/>
+    <col min="3" max="4" width="20.7109375" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" customWidth="1"/>
+    <col min="6" max="7" width="20.7109375" customWidth="1"/>
+    <col min="8" max="8" width="30.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="34" customHeight="1">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" spans="1:8" ht="40" customHeight="1">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" spans="1:8" ht="38" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+    </row>
+    <row r="5" spans="1:8" ht="28" customHeight="1">
+      <c r="A5" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+    </row>
+    <row r="6" spans="1:8" ht="40" customHeight="1">
+      <c r="A6" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="45" customHeight="1">
+      <c r="A7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="7">
+        <v>16.81264811113</v>
+      </c>
+      <c r="D7" s="4">
+        <v>100</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0.653513343284</v>
+      </c>
+      <c r="F7" s="7">
+        <v>14.659001371934</v>
+      </c>
+      <c r="G7" s="7">
+        <v>24.15578572</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="45" customHeight="1">
+      <c r="A8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="7">
+        <v>17.2083674392</v>
+      </c>
+      <c r="D8" s="4">
+        <v>100</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0.675254389727</v>
+      </c>
+      <c r="F8" s="7">
+        <v>14.98568778713</v>
+      </c>
+      <c r="G8" s="7">
+        <v>26.64002224</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="45" customHeight="1">
+      <c r="A9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="7">
+        <v>17.66683273383</v>
+      </c>
+      <c r="D9" s="4">
+        <v>100</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.690407388888</v>
+      </c>
+      <c r="F9" s="7">
+        <v>15.55320039561</v>
+      </c>
+      <c r="G9" s="7">
+        <v>25.05820484</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="45" customHeight="1">
+      <c r="A10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="7">
+        <v>17.4235311056</v>
+      </c>
+      <c r="D10" s="4">
+        <v>100</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.689562769167</v>
+      </c>
+      <c r="F10" s="7">
+        <v>15.2649956211</v>
+      </c>
+      <c r="G10" s="7">
+        <v>27.09175617</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="45" customHeight="1">
+      <c r="A11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="7">
+        <v>54.50497163930999</v>
+      </c>
+      <c r="D11" s="4">
+        <v>100</v>
+      </c>
+      <c r="E11" s="7">
+        <v>3.010561498714</v>
+      </c>
+      <c r="F11" s="7">
+        <v>34.37448410885</v>
+      </c>
+      <c r="G11" s="7">
+        <v>66.57111264</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="45" customHeight="1">
+      <c r="A12" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="7">
+        <v>58.201283144</v>
+      </c>
+      <c r="D12" s="4">
+        <v>100</v>
+      </c>
+      <c r="E12" s="7">
+        <v>2.996312875285</v>
+      </c>
+      <c r="F12" s="7">
+        <v>38.43288652542</v>
+      </c>
+      <c r="G12" s="7">
+        <v>69.86197643</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="45" customHeight="1">
+      <c r="A13" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="7">
+        <v>47.25469538884</v>
+      </c>
+      <c r="D13" s="4">
+        <v>100</v>
+      </c>
+      <c r="E13" s="7">
+        <v>2.675081919836</v>
+      </c>
+      <c r="F13" s="7">
+        <v>29.71202555179</v>
+      </c>
+      <c r="G13" s="7">
+        <v>56.89672242</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="45" customHeight="1">
+      <c r="A14" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="7">
+        <v>50.90068114483</v>
+      </c>
+      <c r="D14" s="4">
+        <v>100</v>
+      </c>
+      <c r="E14" s="7">
+        <v>2.805820850935</v>
+      </c>
+      <c r="F14" s="7">
+        <v>31.61299917308</v>
+      </c>
+      <c r="G14" s="7">
+        <v>61.17425436</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="45" customHeight="1">
+      <c r="A15" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="7">
+        <v>5.376450884124</v>
+      </c>
+      <c r="D15" s="4">
+        <v>100</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0.2980301282526</v>
+      </c>
+      <c r="F15" s="7">
+        <v>4.984806000615</v>
+      </c>
+      <c r="G15" s="7">
+        <v>6.04477203</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="45" customHeight="1">
+      <c r="A16" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="7">
+        <v>5.291779501674</v>
+      </c>
+      <c r="D16" s="4">
+        <v>100</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.2874627067643</v>
+      </c>
+      <c r="F16" s="7">
+        <v>4.907486991115</v>
+      </c>
+      <c r="G16" s="7">
+        <v>7.29747341</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="45" customHeight="1">
+      <c r="A17" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="7">
+        <v>4.993702343056</v>
+      </c>
+      <c r="D17" s="4">
+        <v>100</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0.2973840962944</v>
+      </c>
+      <c r="F17" s="7">
+        <v>4.555181305722</v>
+      </c>
+      <c r="G17" s="7">
+        <v>6.71977696</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="45" customHeight="1">
+      <c r="A18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="7">
+        <v>4.901756139286</v>
+      </c>
       <c r="D18" s="4">
-        <v>135</v>
-      </c>
-      <c r="E18" s="6">
-        <v>9.859923063903704</v>
-      </c>
-      <c r="F18" s="6">
-        <v>9.151532390274074</v>
-      </c>
-      <c r="G18" s="5">
-        <f>IF(AND(ISNUMBER(E18),ISNUMBER(F18),E18&lt;&gt;0),(E18-F18)/E18,"待補")</f>
-        <v>0.07184545650492803</v>
+        <v>100</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.2756560181046</v>
+      </c>
+      <c r="F18" s="7">
+        <v>4.498764577382</v>
+      </c>
+      <c r="G18" s="7">
+        <v>8.32219845</v>
       </c>
       <c r="H18" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="45" customHeight="1">
+      <c r="A19" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="7">
+        <v>123.2346789297831</v>
+      </c>
+      <c r="D19" s="4">
+        <v>83</v>
+      </c>
+      <c r="E19" s="7">
+        <v>2.638986240954819</v>
+      </c>
+      <c r="F19" s="7">
+        <v>123.9392307287337</v>
+      </c>
+      <c r="G19" s="7">
+        <v>6.01696067</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="45" customHeight="1">
+      <c r="A20" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="7">
+        <v>123.2346789297831</v>
+      </c>
+      <c r="D20" s="4">
+        <v>83</v>
+      </c>
+      <c r="E20" s="7">
+        <v>2.638986240954819</v>
+      </c>
+      <c r="F20" s="7">
+        <v>123.9392307287337</v>
+      </c>
+      <c r="G20" s="7">
+        <v>6.60275653</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="45" customHeight="1">
+      <c r="A21" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="7">
+        <v>299.4917599032963</v>
+      </c>
+      <c r="D21" s="4">
+        <v>81</v>
+      </c>
+      <c r="E21" s="7">
+        <v>11.59766951236</v>
+      </c>
+      <c r="F21" s="7">
+        <v>303.268721948937</v>
+      </c>
+      <c r="G21" s="7">
+        <v>6.25656317</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="45" customHeight="1">
+      <c r="A22" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="7">
+        <v>252.1680517323086</v>
+      </c>
+      <c r="D22" s="4">
+        <v>81</v>
+      </c>
+      <c r="E22" s="7">
+        <v>9.392364444529136</v>
+      </c>
+      <c r="F22" s="7">
+        <v>255.1452830486901</v>
+      </c>
+      <c r="G22" s="7">
+        <v>7.46682261</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="45" customHeight="1">
+      <c r="A23" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="7">
+        <v>12.62093021071654</v>
+      </c>
+      <c r="D23" s="4">
+        <v>127</v>
+      </c>
+      <c r="E23" s="7">
+        <v>0.8363256751958268</v>
+      </c>
+      <c r="F23" s="7">
+        <v>11.09438364595748</v>
+      </c>
+      <c r="G23" s="7">
+        <v>2.37528938</v>
+      </c>
+      <c r="H23" s="4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="46" customHeight="1">
-      <c r="A21" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-    </row>
-    <row r="23" spans="1:8" ht="46" customHeight="1">
-      <c r="A23" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-    </row>
-    <row r="25" spans="1:8" ht="42" customHeight="1">
-      <c r="A25" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-    </row>
-    <row r="27" spans="1:8" ht="28" customHeight="1">
-      <c r="A27" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-    </row>
-    <row r="28" spans="1:8" ht="38" customHeight="1">
-      <c r="A28" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-    </row>
-    <row r="29" spans="1:8" ht="52" customHeight="1">
+    <row r="24" spans="1:8" ht="45" customHeight="1">
+      <c r="A24" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="7">
+        <v>10.97050868271654</v>
+      </c>
+      <c r="D24" s="4">
+        <v>127</v>
+      </c>
+      <c r="E24" s="7">
+        <v>0.7161741301438582</v>
+      </c>
+      <c r="F24" s="7">
+        <v>9.726951540952756</v>
+      </c>
+      <c r="G24" s="7">
+        <v>2.804647686666667</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="45" customHeight="1">
+      <c r="A25" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="7">
+        <v>10.72940896452414</v>
+      </c>
+      <c r="D25" s="4">
+        <v>145</v>
+      </c>
+      <c r="E25" s="7">
+        <v>0.6919629266255173</v>
+      </c>
+      <c r="F25" s="7">
+        <v>9.439785611420689</v>
+      </c>
+      <c r="G25" s="7">
+        <v>2.443533233333333</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="45" customHeight="1">
+      <c r="A26" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="7">
+        <v>9.095719413689656</v>
+      </c>
+      <c r="D26" s="4">
+        <v>145</v>
+      </c>
+      <c r="E26" s="7">
+        <v>0.53536225928</v>
+      </c>
+      <c r="F26" s="7">
+        <v>8.136594117781378</v>
+      </c>
+      <c r="G26" s="7">
+        <v>3.046398766666667</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="42" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -1749,19 +3601,592 @@
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
     </row>
+    <row r="31" spans="1:8" ht="28" customHeight="1">
+      <c r="A31" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+    </row>
+    <row r="32" spans="1:8" ht="40" customHeight="1">
+      <c r="A32" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="45" customHeight="1">
+      <c r="A33" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B33" s="4">
+        <v>0</v>
+      </c>
+      <c r="C33" s="4">
+        <v>0</v>
+      </c>
+      <c r="D33" s="4">
+        <v>100</v>
+      </c>
+      <c r="E33" s="7">
+        <v>16.81264811113</v>
+      </c>
+      <c r="F33" s="7">
+        <v>17.66683273383</v>
+      </c>
+      <c r="G33" s="6">
+        <f>IF(AND(ISNUMBER(E33),ISNUMBER(F33),E33&lt;&gt;0),(E33-F33)/E33,"待補")</f>
+        <v>-0.050806072728931416</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="45" customHeight="1">
+      <c r="A34" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B34" s="4">
+        <v>0</v>
+      </c>
+      <c r="C34" s="4">
+        <v>0</v>
+      </c>
+      <c r="D34" s="4">
+        <v>100</v>
+      </c>
+      <c r="E34" s="7">
+        <v>17.2083674392</v>
+      </c>
+      <c r="F34" s="7">
+        <v>17.4235311056</v>
+      </c>
+      <c r="G34" s="6">
+        <f>IF(AND(ISNUMBER(E34),ISNUMBER(F34),E34&lt;&gt;0),(E34-F34)/E34,"待補")</f>
+        <v>-0.012503432830581362</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="45" customHeight="1">
+      <c r="A35" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B35" s="4">
+        <v>0</v>
+      </c>
+      <c r="C35" s="4">
+        <v>0</v>
+      </c>
+      <c r="D35" s="4">
+        <v>100</v>
+      </c>
+      <c r="E35" s="7">
+        <v>16.81264811113</v>
+      </c>
+      <c r="F35" s="7">
+        <v>17.2083674392</v>
+      </c>
+      <c r="G35" s="6">
+        <f>IF(AND(ISNUMBER(E35),ISNUMBER(F35),E35&lt;&gt;0),(E35-F35)/E35,"待補")</f>
+        <v>-0.02353700175334276</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="45" customHeight="1">
+      <c r="A36" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B36" s="4">
+        <v>0</v>
+      </c>
+      <c r="C36" s="4">
+        <v>0</v>
+      </c>
+      <c r="D36" s="4">
+        <v>100</v>
+      </c>
+      <c r="E36" s="7">
+        <v>17.66683273383</v>
+      </c>
+      <c r="F36" s="7">
+        <v>17.4235311056</v>
+      </c>
+      <c r="G36" s="6">
+        <f>IF(AND(ISNUMBER(E36),ISNUMBER(F36),E36&lt;&gt;0),(E36-F36)/E36,"待補")</f>
+        <v>0.013771660823170901</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="45" customHeight="1">
+      <c r="A37" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B37" s="4">
+        <v>8</v>
+      </c>
+      <c r="C37" s="4">
+        <v>4</v>
+      </c>
+      <c r="D37" s="4">
+        <v>29</v>
+      </c>
+      <c r="E37" s="7">
+        <v>24.32021919555172</v>
+      </c>
+      <c r="F37" s="7">
+        <v>23.77076075117241</v>
+      </c>
+      <c r="G37" s="6">
+        <f>IF(AND(ISNUMBER(E37),ISNUMBER(F37),E37&lt;&gt;0),(E37-F37)/E37,"待補")</f>
+        <v>0.02259266003983248</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="45" customHeight="1">
+      <c r="A38" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B38" s="4">
+        <v>9</v>
+      </c>
+      <c r="C38" s="4">
+        <v>3</v>
+      </c>
+      <c r="D38" s="4">
+        <v>25</v>
+      </c>
+      <c r="E38" s="7">
+        <v>24.426966728</v>
+      </c>
+      <c r="F38" s="7">
+        <v>24.24613362052</v>
+      </c>
+      <c r="G38" s="6">
+        <f>IF(AND(ISNUMBER(E38),ISNUMBER(F38),E38&lt;&gt;0),(E38-F38)/E38,"待補")</f>
+        <v>0.007403011167682776</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="45" customHeight="1">
+      <c r="A39" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B39" s="4">
+        <v>7</v>
+      </c>
+      <c r="C39" s="4">
+        <v>12</v>
+      </c>
+      <c r="D39" s="4">
+        <v>21</v>
+      </c>
+      <c r="E39" s="7">
+        <v>21.7729943357619</v>
+      </c>
+      <c r="F39" s="7">
+        <v>20.28276458571429</v>
+      </c>
+      <c r="G39" s="6">
+        <f>IF(AND(ISNUMBER(E39),ISNUMBER(F39),E39&lt;&gt;0),(E39-F39)/E39,"待補")</f>
+        <v>0.06844395066047179</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="45" customHeight="1">
+      <c r="A40" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B40" s="4">
+        <v>9</v>
+      </c>
+      <c r="C40" s="4">
+        <v>12</v>
+      </c>
+      <c r="D40" s="4">
+        <v>25</v>
+      </c>
+      <c r="E40" s="7">
+        <v>22.59478257216</v>
+      </c>
+      <c r="F40" s="7">
+        <v>21.56710227932</v>
+      </c>
+      <c r="G40" s="6">
+        <f>IF(AND(ISNUMBER(E40),ISNUMBER(F40),E40&lt;&gt;0),(E40-F40)/E40,"待補")</f>
+        <v>0.04548307953652312</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="45" customHeight="1">
+      <c r="A41" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B41" s="4">
+        <v>0</v>
+      </c>
+      <c r="C41" s="4">
+        <v>0</v>
+      </c>
+      <c r="D41" s="4">
+        <v>100</v>
+      </c>
+      <c r="E41" s="7">
+        <v>5.376450884124</v>
+      </c>
+      <c r="F41" s="7">
+        <v>4.993702343056</v>
+      </c>
+      <c r="G41" s="6">
+        <f>IF(AND(ISNUMBER(E41),ISNUMBER(F41),E41&lt;&gt;0),(E41-F41)/E41,"待補")</f>
+        <v>0.07118981449234645</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="45" customHeight="1">
+      <c r="A42" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B42" s="4">
+        <v>0</v>
+      </c>
+      <c r="C42" s="4">
+        <v>0</v>
+      </c>
+      <c r="D42" s="4">
+        <v>100</v>
+      </c>
+      <c r="E42" s="7">
+        <v>5.291779501674</v>
+      </c>
+      <c r="F42" s="7">
+        <v>4.901756139286</v>
+      </c>
+      <c r="G42" s="6">
+        <f>IF(AND(ISNUMBER(E42),ISNUMBER(F42),E42&lt;&gt;0),(E42-F42)/E42,"待補")</f>
+        <v>0.07370363074739225</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="45" customHeight="1">
+      <c r="A43" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B43" s="4">
+        <v>0</v>
+      </c>
+      <c r="C43" s="4">
+        <v>0</v>
+      </c>
+      <c r="D43" s="4">
+        <v>100</v>
+      </c>
+      <c r="E43" s="7">
+        <v>5.376450884124</v>
+      </c>
+      <c r="F43" s="7">
+        <v>5.291779501674</v>
+      </c>
+      <c r="G43" s="6">
+        <f>IF(AND(ISNUMBER(E43),ISNUMBER(F43),E43&lt;&gt;0),(E43-F43)/E43,"待補")</f>
+        <v>0.015748564299178053</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="45" customHeight="1">
+      <c r="A44" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B44" s="4">
+        <v>0</v>
+      </c>
+      <c r="C44" s="4">
+        <v>0</v>
+      </c>
+      <c r="D44" s="4">
+        <v>100</v>
+      </c>
+      <c r="E44" s="7">
+        <v>4.993702343056</v>
+      </c>
+      <c r="F44" s="7">
+        <v>4.901756139286</v>
+      </c>
+      <c r="G44" s="6">
+        <f>IF(AND(ISNUMBER(E44),ISNUMBER(F44),E44&lt;&gt;0),(E44-F44)/E44,"待補")</f>
+        <v>0.018412431789783346</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="45" customHeight="1">
+      <c r="A45" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B45" s="4">
+        <v>6</v>
+      </c>
+      <c r="C45" s="4">
+        <v>13</v>
+      </c>
+      <c r="D45" s="4">
+        <v>63</v>
+      </c>
+      <c r="E45" s="7">
+        <v>6.914644631380952</v>
+      </c>
+      <c r="F45" s="7">
+        <v>7.018932233142857</v>
+      </c>
+      <c r="G45" s="6">
+        <f>IF(AND(ISNUMBER(E45),ISNUMBER(F45),E45&lt;&gt;0),(E45-F45)/E45,"待補")</f>
+        <v>-0.015082134704163098</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="45" customHeight="1">
+      <c r="A46" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B46" s="4">
+        <v>6</v>
+      </c>
+      <c r="C46" s="4">
+        <v>12</v>
+      </c>
+      <c r="D46" s="4">
+        <v>64</v>
+      </c>
+      <c r="E46" s="7">
+        <v>7.010373222453126</v>
+      </c>
+      <c r="F46" s="7">
+        <v>7.11722529434375</v>
+      </c>
+      <c r="G46" s="6">
+        <f>IF(AND(ISNUMBER(E46),ISNUMBER(F46),E46&lt;&gt;0),(E46-F46)/E46,"待補")</f>
+        <v>-0.015241994755485188</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="45" customHeight="1">
+      <c r="A47" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B47" s="4">
+        <v>0</v>
+      </c>
+      <c r="C47" s="4">
+        <v>0</v>
+      </c>
+      <c r="D47" s="4">
+        <v>76</v>
+      </c>
+      <c r="E47" s="7">
+        <v>8.705992042526315</v>
+      </c>
+      <c r="F47" s="7">
+        <v>8.705992042526315</v>
+      </c>
+      <c r="G47" s="6">
+        <f>IF(AND(ISNUMBER(E47),ISNUMBER(F47),E47&lt;&gt;0),(E47-F47)/E47,"待補")</f>
+        <v>0.0</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="45" customHeight="1">
+      <c r="A48" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B48" s="4">
+        <v>1</v>
+      </c>
+      <c r="C48" s="4">
+        <v>0</v>
+      </c>
+      <c r="D48" s="4">
+        <v>69</v>
+      </c>
+      <c r="E48" s="7">
+        <v>7.395330353434783</v>
+      </c>
+      <c r="F48" s="7">
+        <v>7.395330353434783</v>
+      </c>
+      <c r="G48" s="6">
+        <f>IF(AND(ISNUMBER(E48),ISNUMBER(F48),E48&lt;&gt;0),(E48-F48)/E48,"待補")</f>
+        <v>0.0</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="45" customHeight="1">
+      <c r="A49" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B49" s="4">
+        <v>28</v>
+      </c>
+      <c r="C49" s="4">
+        <v>4</v>
+      </c>
+      <c r="D49" s="4">
+        <v>110</v>
+      </c>
+      <c r="E49" s="7">
+        <v>9.489490134990909</v>
+      </c>
+      <c r="F49" s="7">
+        <v>8.842029700663637</v>
+      </c>
+      <c r="G49" s="6">
+        <f>IF(AND(ISNUMBER(E49),ISNUMBER(F49),E49&lt;&gt;0),(E49-F49)/E49,"待補")</f>
+        <v>0.06822921201423354</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="45" customHeight="1">
+      <c r="A50" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B50" s="4">
+        <v>25</v>
+      </c>
+      <c r="C50" s="4">
+        <v>2</v>
+      </c>
+      <c r="D50" s="4">
+        <v>119</v>
+      </c>
+      <c r="E50" s="7">
+        <v>9.519133282310923</v>
+      </c>
+      <c r="F50" s="7">
+        <v>8.297936695739496</v>
+      </c>
+      <c r="G50" s="6">
+        <f>IF(AND(ISNUMBER(E50),ISNUMBER(F50),E50&lt;&gt;0),(E50-F50)/E50,"待補")</f>
+        <v>0.1282886319955973</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="45" customHeight="1">
+      <c r="A51" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B51" s="4">
+        <v>7</v>
+      </c>
+      <c r="C51" s="4">
+        <v>0</v>
+      </c>
+      <c r="D51" s="4">
+        <v>114</v>
+      </c>
+      <c r="E51" s="7">
+        <v>9.559662507815789</v>
+      </c>
+      <c r="F51" s="7">
+        <v>9.598285944078947</v>
+      </c>
+      <c r="G51" s="6">
+        <f>IF(AND(ISNUMBER(E51),ISNUMBER(F51),E51&lt;&gt;0),(E51-F51)/E51,"待補")</f>
+        <v>-0.004040251026809923</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="45" customHeight="1">
+      <c r="A52" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B52" s="4">
+        <v>6</v>
+      </c>
+      <c r="C52" s="4">
+        <v>0</v>
+      </c>
+      <c r="D52" s="4">
+        <v>138</v>
+      </c>
+      <c r="E52" s="7">
+        <v>9.746082000043478</v>
+      </c>
+      <c r="F52" s="7">
+        <v>8.96531325555797</v>
+      </c>
+      <c r="G52" s="6">
+        <f>IF(AND(ISNUMBER(E52),ISNUMBER(F52),E52&lt;&gt;0),(E52-F52)/E52,"待補")</f>
+        <v>0.08011103790036085</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="6">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A21:H21"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A25:H25"/>
-    <mergeCell ref="A27:H27"/>
-    <mergeCell ref="A28:H28"/>
     <mergeCell ref="A29:H29"/>
+    <mergeCell ref="A31:H31"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.4" bottom="0.4" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" fitToHeight="0" orientation="landscape"/>

--- a/results/six_week_reports_20261028/report_01_CN距離容差與Solver.xlsx
+++ b/results/six_week_reports_20261028/report_01_CN距離容差與Solver.xlsx
@@ -12,9 +12,9 @@
     <sheet name="精度時間與成對比較" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">四組結果比較!$A$1:$H$73</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">精度時間與成對比較!$A$1:$H$52</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">設定與說明!$A$1:$H$46</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">四組結果比較!$A$1:$H$76</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">精度時間與成對比較!$A$1:$H$79</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">設定與說明!$A$1:$H$63</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">四組結果比較!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">精度時間與成對比較!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">設定與說明!$1:$3</definedName>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="150">
   <si>
     <t>第1次｜CN距離容差與Solver</t>
   </si>
@@ -252,6 +252,75 @@
     <t>論文TableI的ETH e_p=15.3427cm，Tongji Plot1～4=5.2558/11.4808/4.8756/4.3560cm，各報100%；分母與成功門檻待補。四組本地控制實驗不是作者程式重跑；目前結果不支持「這兩項改動在所有場景都改善」。</t>
   </si>
   <si>
+    <t>原論文與本地四組：只列本週重要設定</t>
+  </si>
+  <si>
+    <t>原論文</t>
+  </si>
+  <si>
+    <t>本地修改前</t>
+  </si>
+  <si>
+    <t>本地修改後</t>
+  </si>
+  <si>
+    <t>不是成功門檻或voxel尺寸</t>
+  </si>
+  <si>
+    <t>剛體Solver</t>
+  </si>
+  <si>
+    <t>Euclidean transform；細節未交代</t>
+  </si>
+  <si>
+    <t>論文未說明，不把SVD稱作作者原始實作</t>
+  </si>
+  <si>
+    <t>新增弱配對補救</t>
+  </si>
+  <si>
+    <t>未描述本地evidence recovery</t>
+  </si>
+  <si>
+    <t>論文本身的triangle fallback仍在；與新增補救不同</t>
+  </si>
+  <si>
+    <t>N／w／Thscore</t>
+  </si>
+  <si>
+    <t>183／10／40</t>
+  </si>
+  <si>
+    <t>三項固定；沒有新增第三個實驗變數</t>
+  </si>
+  <si>
+    <t>論文時間與缺值原因：只作報告值參考</t>
+  </si>
+  <si>
+    <t>論文matching ms</t>
+  </si>
+  <si>
+    <t>論文total s</t>
+  </si>
+  <si>
+    <t>論文e_R／e_t</t>
+  </si>
+  <si>
+    <t>論文成功分母／門檻</t>
+  </si>
+  <si>
+    <t>時間可比性</t>
+  </si>
+  <si>
+    <t>未單獨報告；Table I用e_p</t>
+  </si>
+  <si>
+    <t>待補：本文未明確交代</t>
+  </si>
+  <si>
+    <t>i7-9700F 3GHz；實際threads未交代；本地計時範圍不同，不算加速比</t>
+  </si>
+  <si>
     <t>數據來源與比較限制</t>
   </si>
   <si>
@@ -379,6 +448,33 @@
   </si>
   <si>
     <t>ETH-tree；10cm固定；SVD→RANSAC</t>
+  </si>
+  <si>
+    <t>四組直接對照論文與修改前5cm/SVD；誤差下降率正值為降低、負值為變大</t>
+  </si>
+  <si>
+    <t>本地e_p cm</t>
+  </si>
+  <si>
+    <t>vs論文誤差下降率</t>
+  </si>
+  <si>
+    <t>vs修改前誤差下降率</t>
+  </si>
+  <si>
+    <t>vs論文成功率 pp</t>
+  </si>
+  <si>
+    <t>vs修改前成功率 pp</t>
+  </si>
+  <si>
+    <t>不可比：本地缺變換；有限N見前表</t>
+  </si>
+  <si>
+    <t>不可比：前後有限案例集合不同</t>
+  </si>
+  <si>
+    <t>vs論文是報告值的算術差異，並非同門檻／同配對的公平重跑。論文e_R/e_t未單獨報告、成功分母與門檻待補；不能由e_p推算。缺變換不是漏做實驗，也不能填0；前後有限集合不同請看共同成功對照。時間範圍不同不列下降率。</t>
   </si>
 </sst>
 </file>
@@ -463,7 +559,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -478,49 +574,52 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="170" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="171" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="172" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="173" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="174" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="175" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1286,14 +1385,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>752475</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1316,13 +1415,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
+      <xdr:row>54</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>752475</xdr:colOff>
-      <xdr:row>67</xdr:row>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>69</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -1637,11 +1736,8 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="27.7109375" customWidth="1"/>
-    <col min="2" max="2" width="21.7109375" customWidth="1"/>
-    <col min="3" max="4" width="20.7109375" customWidth="1"/>
-    <col min="5" max="5" width="18.7109375" customWidth="1"/>
-    <col min="6" max="7" width="20.7109375" customWidth="1"/>
-    <col min="8" max="8" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="8" width="24.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="34" customHeight="1">
@@ -2164,7 +2260,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="27.7109375" customWidth="1"/>
@@ -2237,7 +2333,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="45" customHeight="1">
+    <row r="7" spans="1:8" ht="60" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>28</v>
       </c>
@@ -2279,7 +2375,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="45" customHeight="1">
+    <row r="10" spans="1:8" ht="78" customHeight="1">
       <c r="A10" s="4" t="s">
         <v>39</v>
       </c>
@@ -2341,13 +2437,13 @@
       <c r="C15" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="F15" s="19">
+      <c r="F15" s="20">
         <f>(100/100-100/100)*100</f>
         <v>0.0</v>
       </c>
@@ -2368,13 +2464,13 @@
       <c r="C16" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="F16" s="19">
+      <c r="F16" s="20">
         <f>(100/100-100/100)*100</f>
         <v>0.0</v>
       </c>
@@ -2395,13 +2491,13 @@
       <c r="C17" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="F17" s="19">
+      <c r="F17" s="20">
         <f>(100/100-100/100)*100</f>
         <v>0.0</v>
       </c>
@@ -2422,13 +2518,13 @@
       <c r="C18" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="F18" s="19">
+      <c r="F18" s="20">
         <f>(100/100-100/100)*100</f>
         <v>0.0</v>
       </c>
@@ -2449,13 +2545,13 @@
       <c r="C19" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="F19" s="19">
+      <c r="F19" s="20">
         <f>(37/100-33/100)*100</f>
         <v>3.9999999999999982</v>
       </c>
@@ -2476,13 +2572,13 @@
       <c r="C20" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="F20" s="19">
+      <c r="F20" s="20">
         <f>(34/100-28/100)*100</f>
         <v>6.0</v>
       </c>
@@ -2503,13 +2599,13 @@
       <c r="C21" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="F21" s="19">
+      <c r="F21" s="20">
         <f>(28/100-33/100)*100</f>
         <v>-4.999999999999999</v>
       </c>
@@ -2530,13 +2626,13 @@
       <c r="C22" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="F22" s="19">
+      <c r="F22" s="20">
         <f>(34/100-37/100)*100</f>
         <v>-2.9999999999999973</v>
       </c>
@@ -2557,13 +2653,13 @@
       <c r="C23" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="F23" s="19">
+      <c r="F23" s="20">
         <f>(100/100-100/100)*100</f>
         <v>0.0</v>
       </c>
@@ -2584,13 +2680,13 @@
       <c r="C24" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="F24" s="19">
+      <c r="F24" s="20">
         <f>(100/100-100/100)*100</f>
         <v>0.0</v>
       </c>
@@ -2611,13 +2707,13 @@
       <c r="C25" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E25" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="F25" s="19">
+      <c r="F25" s="20">
         <f>(100/100-100/100)*100</f>
         <v>0.0</v>
       </c>
@@ -2638,13 +2734,13 @@
       <c r="C26" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E26" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="F26" s="19">
+      <c r="F26" s="20">
         <f>(100/100-100/100)*100</f>
         <v>0.0</v>
       </c>
@@ -2665,13 +2761,13 @@
       <c r="C27" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="E27" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="F27" s="19">
+      <c r="F27" s="20">
         <f>(69/100-76/100)*100</f>
         <v>-7.000000000000006</v>
       </c>
@@ -2692,13 +2788,13 @@
       <c r="C28" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E28" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="F28" s="19">
+      <c r="F28" s="20">
         <f>(70/100-76/100)*100</f>
         <v>-6.000000000000005</v>
       </c>
@@ -2719,13 +2815,13 @@
       <c r="C29" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="E29" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="F29" s="19">
+      <c r="F29" s="20">
         <f>(76/100-76/100)*100</f>
         <v>0.0</v>
       </c>
@@ -2746,13 +2842,13 @@
       <c r="C30" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="E30" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="F30" s="19">
+      <c r="F30" s="20">
         <f>(70/100-69/100)*100</f>
         <v>1.0000000000000009</v>
       </c>
@@ -2773,13 +2869,13 @@
       <c r="C31" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="E31" s="4" t="s">
+      <c r="E31" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="F31" s="19">
+      <c r="F31" s="20">
         <f>(138/150-114/150)*100</f>
         <v>16.000000000000004</v>
       </c>
@@ -2800,13 +2896,13 @@
       <c r="C32" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="E32" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="F32" s="19">
+      <c r="F32" s="20">
         <f>(144/150-121/150)*100</f>
         <v>15.333333333333332</v>
       </c>
@@ -2827,13 +2923,13 @@
       <c r="C33" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D33" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="E33" s="4" t="s">
+      <c r="E33" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="F33" s="19">
+      <c r="F33" s="20">
         <f>(121/150-114/150)*100</f>
         <v>4.666666666666663</v>
       </c>
@@ -2854,13 +2950,13 @@
       <c r="C34" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="E34" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="F34" s="19">
+      <c r="F34" s="20">
         <f>(144/150-138/150)*100</f>
         <v>3.9999999999999925</v>
       </c>
@@ -2919,44 +3015,273 @@
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
     </row>
-    <row r="44" spans="1:8" ht="38" customHeight="1">
-      <c r="A44" s="2" t="s">
+    <row r="44" spans="1:8" ht="40" customHeight="1">
+      <c r="A44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B44" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2"/>
-    </row>
-    <row r="45" spans="1:8" ht="38" customHeight="1">
-      <c r="A45" s="2" t="s">
+      <c r="C44" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
-    </row>
-    <row r="46" spans="1:8" ht="52" customHeight="1">
-      <c r="A46" s="2" t="s">
+      <c r="D44" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
+      <c r="E44" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="45" customHeight="1">
+      <c r="A45" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="60" customHeight="1">
+      <c r="A46" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="78" customHeight="1">
+      <c r="A47" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="60" customHeight="1">
+      <c r="A48" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="28" customHeight="1">
+      <c r="A51" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B51" s="3"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
+      <c r="H51" s="3"/>
+    </row>
+    <row r="52" spans="1:8" ht="40" customHeight="1">
+      <c r="A52" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="96" customHeight="1">
+      <c r="A53" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B53" s="7">
+        <v>20.718</v>
+      </c>
+      <c r="C53" s="7">
+        <v>11.657</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="96" customHeight="1">
+      <c r="A54" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B54" s="7">
+        <v>30.699</v>
+      </c>
+      <c r="C54" s="7">
+        <v>16.712</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="96" customHeight="1">
+      <c r="A55" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55" s="7">
+        <v>4.5596</v>
+      </c>
+      <c r="C55" s="7">
+        <v>8.3584</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="96" customHeight="1">
+      <c r="A56" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B56" s="7">
+        <v>19.522</v>
+      </c>
+      <c r="C56" s="7">
+        <v>9.451599999999999</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="96" customHeight="1">
+      <c r="A57" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B57" s="7">
+        <v>3.0405</v>
+      </c>
+      <c r="C57" s="7">
+        <v>8.699199999999999</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="28" customHeight="1">
+      <c r="A60" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B60" s="3"/>
+      <c r="C60" s="3"/>
+      <c r="D60" s="3"/>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3"/>
+      <c r="G60" s="3"/>
+      <c r="H60" s="3"/>
+    </row>
+    <row r="61" spans="1:8" ht="38" customHeight="1">
+      <c r="A61" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="2"/>
+      <c r="F61" s="2"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="2"/>
+    </row>
+    <row r="62" spans="1:8" ht="38" customHeight="1">
+      <c r="A62" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="2"/>
+      <c r="E62" s="2"/>
+      <c r="F62" s="2"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="2"/>
+    </row>
+    <row r="63" spans="1:8" ht="52" customHeight="1">
+      <c r="A63" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B63" s="2"/>
+      <c r="C63" s="2"/>
+      <c r="D63" s="2"/>
+      <c r="E63" s="2"/>
+      <c r="F63" s="2"/>
+      <c r="G63" s="2"/>
+      <c r="H63" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="14">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A3:H3"/>
@@ -2966,9 +3291,11 @@
     <mergeCell ref="A39:H39"/>
     <mergeCell ref="A41:H41"/>
     <mergeCell ref="A43:H43"/>
-    <mergeCell ref="A44:H44"/>
-    <mergeCell ref="A45:H45"/>
-    <mergeCell ref="A46:H46"/>
+    <mergeCell ref="A51:H51"/>
+    <mergeCell ref="A60:H60"/>
+    <mergeCell ref="A61:H61"/>
+    <mergeCell ref="A62:H62"/>
+    <mergeCell ref="A63:H63"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.4" bottom="0.4" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" fitToHeight="0" orientation="landscape"/>
@@ -2984,7 +3311,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="27.7109375" customWidth="1"/>
@@ -3033,7 +3360,7 @@
     </row>
     <row r="5" spans="1:8" ht="28" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -3048,25 +3375,25 @@
         <v>44</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>86</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="45" customHeight="1">
@@ -3091,7 +3418,7 @@
       <c r="G7" s="7">
         <v>24.15578572</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="19" t="s">
         <v>54</v>
       </c>
     </row>
@@ -3117,7 +3444,7 @@
       <c r="G8" s="7">
         <v>26.64002224</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="19" t="s">
         <v>54</v>
       </c>
     </row>
@@ -3143,7 +3470,7 @@
       <c r="G9" s="7">
         <v>25.05820484</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="19" t="s">
         <v>54</v>
       </c>
     </row>
@@ -3169,7 +3496,7 @@
       <c r="G10" s="7">
         <v>27.09175617</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="19" t="s">
         <v>54</v>
       </c>
     </row>
@@ -3195,7 +3522,7 @@
       <c r="G11" s="7">
         <v>66.57111264</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="H11" s="19" t="s">
         <v>61</v>
       </c>
     </row>
@@ -3221,7 +3548,7 @@
       <c r="G12" s="7">
         <v>69.86197643</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="H12" s="19" t="s">
         <v>63</v>
       </c>
     </row>
@@ -3247,7 +3574,7 @@
       <c r="G13" s="7">
         <v>56.89672242</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="H13" s="19" t="s">
         <v>62</v>
       </c>
     </row>
@@ -3273,7 +3600,7 @@
       <c r="G14" s="7">
         <v>61.17425436</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="H14" s="19" t="s">
         <v>64</v>
       </c>
     </row>
@@ -3299,7 +3626,7 @@
       <c r="G15" s="7">
         <v>6.04477203</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="H15" s="19" t="s">
         <v>54</v>
       </c>
     </row>
@@ -3325,7 +3652,7 @@
       <c r="G16" s="7">
         <v>7.29747341</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="H16" s="19" t="s">
         <v>54</v>
       </c>
     </row>
@@ -3351,7 +3678,7 @@
       <c r="G17" s="7">
         <v>6.71977696</v>
       </c>
-      <c r="H17" s="4" t="s">
+      <c r="H17" s="19" t="s">
         <v>54</v>
       </c>
     </row>
@@ -3377,7 +3704,7 @@
       <c r="G18" s="7">
         <v>8.32219845</v>
       </c>
-      <c r="H18" s="4" t="s">
+      <c r="H18" s="19" t="s">
         <v>54</v>
       </c>
     </row>
@@ -3403,7 +3730,7 @@
       <c r="G19" s="7">
         <v>6.01696067</v>
       </c>
-      <c r="H19" s="4" t="s">
+      <c r="H19" s="19" t="s">
         <v>65</v>
       </c>
     </row>
@@ -3429,7 +3756,7 @@
       <c r="G20" s="7">
         <v>6.60275653</v>
       </c>
-      <c r="H20" s="4" t="s">
+      <c r="H20" s="19" t="s">
         <v>65</v>
       </c>
     </row>
@@ -3455,7 +3782,7 @@
       <c r="G21" s="7">
         <v>6.25656317</v>
       </c>
-      <c r="H21" s="4" t="s">
+      <c r="H21" s="19" t="s">
         <v>66</v>
       </c>
     </row>
@@ -3481,7 +3808,7 @@
       <c r="G22" s="7">
         <v>7.46682261</v>
       </c>
-      <c r="H22" s="4" t="s">
+      <c r="H22" s="19" t="s">
         <v>67</v>
       </c>
     </row>
@@ -3507,7 +3834,7 @@
       <c r="G23" s="7">
         <v>2.37528938</v>
       </c>
-      <c r="H23" s="4" t="s">
+      <c r="H23" s="19" t="s">
         <v>68</v>
       </c>
     </row>
@@ -3533,7 +3860,7 @@
       <c r="G24" s="7">
         <v>2.804647686666667</v>
       </c>
-      <c r="H24" s="4" t="s">
+      <c r="H24" s="19" t="s">
         <v>70</v>
       </c>
     </row>
@@ -3559,7 +3886,7 @@
       <c r="G25" s="7">
         <v>2.443533233333333</v>
       </c>
-      <c r="H25" s="4" t="s">
+      <c r="H25" s="19" t="s">
         <v>69</v>
       </c>
     </row>
@@ -3585,13 +3912,13 @@
       <c r="G26" s="7">
         <v>3.046398766666667</v>
       </c>
-      <c r="H26" s="4" t="s">
+      <c r="H26" s="19" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="42" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -3603,7 +3930,7 @@
     </row>
     <row r="31" spans="1:8" ht="28" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -3615,33 +3942,33 @@
     </row>
     <row r="32" spans="1:8" ht="40" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>94</v>
+        <v>117</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="45" customHeight="1">
       <c r="A33" s="4" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="B33" s="4">
         <v>0</v>
@@ -3663,12 +3990,12 @@
         <v>-0.050806072728931416</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="45" customHeight="1">
       <c r="A34" s="4" t="s">
-        <v>99</v>
+        <v>122</v>
       </c>
       <c r="B34" s="4">
         <v>0</v>
@@ -3690,12 +4017,12 @@
         <v>-0.012503432830581362</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="45" customHeight="1">
       <c r="A35" s="4" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="B35" s="4">
         <v>0</v>
@@ -3717,12 +4044,12 @@
         <v>-0.02353700175334276</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="45" customHeight="1">
       <c r="A36" s="4" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="B36" s="4">
         <v>0</v>
@@ -3744,12 +4071,12 @@
         <v>0.013771660823170901</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="45" customHeight="1">
       <c r="A37" s="4" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="B37" s="4">
         <v>8</v>
@@ -3771,12 +4098,12 @@
         <v>0.02259266003983248</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="45" customHeight="1">
       <c r="A38" s="4" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="B38" s="4">
         <v>9</v>
@@ -3798,12 +4125,12 @@
         <v>0.007403011167682776</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="45" customHeight="1">
       <c r="A39" s="4" t="s">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="B39" s="4">
         <v>7</v>
@@ -3825,12 +4152,12 @@
         <v>0.06844395066047179</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="45" customHeight="1">
       <c r="A40" s="4" t="s">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="B40" s="4">
         <v>9</v>
@@ -3852,12 +4179,12 @@
         <v>0.04548307953652312</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="45" customHeight="1">
       <c r="A41" s="4" t="s">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="B41" s="4">
         <v>0</v>
@@ -3879,12 +4206,12 @@
         <v>0.07118981449234645</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="45" customHeight="1">
       <c r="A42" s="4" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="B42" s="4">
         <v>0</v>
@@ -3906,12 +4233,12 @@
         <v>0.07370363074739225</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="45" customHeight="1">
       <c r="A43" s="4" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="B43" s="4">
         <v>0</v>
@@ -3933,12 +4260,12 @@
         <v>0.015748564299178053</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="45" customHeight="1">
       <c r="A44" s="4" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="B44" s="4">
         <v>0</v>
@@ -3960,12 +4287,12 @@
         <v>0.018412431789783346</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="45" customHeight="1">
       <c r="A45" s="4" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="B45" s="4">
         <v>6</v>
@@ -3987,12 +4314,12 @@
         <v>-0.015082134704163098</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="45" customHeight="1">
       <c r="A46" s="4" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="B46" s="4">
         <v>6</v>
@@ -4014,12 +4341,12 @@
         <v>-0.015241994755485188</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="45" customHeight="1">
       <c r="A47" s="4" t="s">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="B47" s="4">
         <v>0</v>
@@ -4041,12 +4368,12 @@
         <v>0.0</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="45" customHeight="1">
       <c r="A48" s="4" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="B48" s="4">
         <v>1</v>
@@ -4068,12 +4395,12 @@
         <v>0.0</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="45" customHeight="1">
       <c r="A49" s="4" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="B49" s="4">
         <v>28</v>
@@ -4095,12 +4422,12 @@
         <v>0.06822921201423354</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="45" customHeight="1">
       <c r="A50" s="4" t="s">
-        <v>115</v>
+        <v>138</v>
       </c>
       <c r="B50" s="4">
         <v>25</v>
@@ -4122,12 +4449,12 @@
         <v>0.1282886319955973</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="45" customHeight="1">
       <c r="A51" s="4" t="s">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="B51" s="4">
         <v>7</v>
@@ -4149,12 +4476,12 @@
         <v>-0.004040251026809923</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="45" customHeight="1">
       <c r="A52" s="4" t="s">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="B52" s="4">
         <v>6</v>
@@ -4176,17 +4503,657 @@
         <v>0.08011103790036085</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>98</v>
-      </c>
+        <v>121</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="28" customHeight="1">
+      <c r="A55" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B55" s="3"/>
+      <c r="C55" s="3"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3"/>
+      <c r="H55" s="3"/>
+    </row>
+    <row r="56" spans="1:8" ht="40" customHeight="1">
+      <c r="A56" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="45" customHeight="1">
+      <c r="A57" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" s="7">
+        <v>5.2558</v>
+      </c>
+      <c r="D57" s="7">
+        <v>16.81264811113</v>
+      </c>
+      <c r="E57" s="6">
+        <f>IF(AND(ISNUMBER(C57),ISNUMBER(D57),C57&lt;&gt;0),(C57-D57)/C57,"不可比")</f>
+        <v>-2.198875168600403</v>
+      </c>
+      <c r="F57" s="6">
+        <f>IF(AND(ISNUMBER(D57),16.81264811113&lt;&gt;0),(16.81264811113-D57)/16.81264811113,"不可比")</f>
+        <v>0.0</v>
+      </c>
+      <c r="G57" s="20">
+        <f>(100/100-1)*100</f>
+        <v>0.0</v>
+      </c>
+      <c r="H57" s="20">
+        <f>(100/100-100/100)*100</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="45" customHeight="1">
+      <c r="A58" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="7">
+        <v>5.2558</v>
+      </c>
+      <c r="D58" s="7">
+        <v>17.2083674392</v>
+      </c>
+      <c r="E58" s="6">
+        <f>IF(AND(ISNUMBER(C58),ISNUMBER(D58),C58&lt;&gt;0),(C58-D58)/C58,"不可比")</f>
+        <v>-2.274167099052476</v>
+      </c>
+      <c r="F58" s="6">
+        <f>IF(AND(ISNUMBER(D58),16.81264811113&lt;&gt;0),(16.81264811113-D58)/16.81264811113,"不可比")</f>
+        <v>-0.02353700175334276</v>
+      </c>
+      <c r="G58" s="20">
+        <f>(100/100-1)*100</f>
+        <v>0.0</v>
+      </c>
+      <c r="H58" s="20">
+        <f>(100/100-100/100)*100</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="45" customHeight="1">
+      <c r="A59" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C59" s="7">
+        <v>5.2558</v>
+      </c>
+      <c r="D59" s="7">
+        <v>17.66683273383</v>
+      </c>
+      <c r="E59" s="6">
+        <f>IF(AND(ISNUMBER(C59),ISNUMBER(D59),C59&lt;&gt;0),(C59-D59)/C59,"不可比")</f>
+        <v>-2.361397453067088</v>
+      </c>
+      <c r="F59" s="6">
+        <f>IF(AND(ISNUMBER(D59),16.81264811113&lt;&gt;0),(16.81264811113-D59)/16.81264811113,"不可比")</f>
+        <v>-0.050806072728931416</v>
+      </c>
+      <c r="G59" s="20">
+        <f>(100/100-1)*100</f>
+        <v>0.0</v>
+      </c>
+      <c r="H59" s="20">
+        <f>(100/100-100/100)*100</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="45" customHeight="1">
+      <c r="A60" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C60" s="7">
+        <v>5.2558</v>
+      </c>
+      <c r="D60" s="7">
+        <v>17.4235311056</v>
+      </c>
+      <c r="E60" s="6">
+        <f>IF(AND(ISNUMBER(C60),ISNUMBER(D60),C60&lt;&gt;0),(C60-D60)/C60,"不可比")</f>
+        <v>-2.3151054274515777</v>
+      </c>
+      <c r="F60" s="6">
+        <f>IF(AND(ISNUMBER(D60),16.81264811113&lt;&gt;0),(16.81264811113-D60)/16.81264811113,"不可比")</f>
+        <v>-0.03633472790438032</v>
+      </c>
+      <c r="G60" s="20">
+        <f>(100/100-1)*100</f>
+        <v>0.0</v>
+      </c>
+      <c r="H60" s="20">
+        <f>(100/100-100/100)*100</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="45" customHeight="1">
+      <c r="A61" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C61" s="7">
+        <v>11.4808</v>
+      </c>
+      <c r="D61" s="7">
+        <v>54.50497163930999</v>
+      </c>
+      <c r="E61" s="6">
+        <f>IF(AND(ISNUMBER(C61),ISNUMBER(D61),C61&lt;&gt;0),(C61-D61)/C61,"不可比")</f>
+        <v>-3.7474889937382407</v>
+      </c>
+      <c r="F61" s="6">
+        <f>IF(AND(ISNUMBER(D61),54.50497163930999&lt;&gt;0),(54.50497163930999-D61)/54.50497163930999,"不可比")</f>
+        <v>0.0</v>
+      </c>
+      <c r="G61" s="20">
+        <f>(33/100-1)*100</f>
+        <v>-67.0</v>
+      </c>
+      <c r="H61" s="20">
+        <f>(33/100-33/100)*100</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="45" customHeight="1">
+      <c r="A62" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="7">
+        <v>11.4808</v>
+      </c>
+      <c r="D62" s="7">
+        <v>58.201283144</v>
+      </c>
+      <c r="E62" s="6">
+        <f>IF(AND(ISNUMBER(C62),ISNUMBER(D62),C62&lt;&gt;0),(C62-D62)/C62,"不可比")</f>
+        <v>-4.069444911852833</v>
+      </c>
+      <c r="F62" s="6">
+        <f>IF(AND(ISNUMBER(D62),54.50497163930999&lt;&gt;0),(54.50497163930999-D62)/54.50497163930999,"不可比")</f>
+        <v>-0.06781604307861266</v>
+      </c>
+      <c r="G62" s="20">
+        <f>(28/100-1)*100</f>
+        <v>-72.0</v>
+      </c>
+      <c r="H62" s="20">
+        <f>(28/100-33/100)*100</f>
+        <v>-4.999999999999999</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="45" customHeight="1">
+      <c r="A63" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C63" s="7">
+        <v>11.4808</v>
+      </c>
+      <c r="D63" s="7">
+        <v>47.25469538884</v>
+      </c>
+      <c r="E63" s="6">
+        <f>IF(AND(ISNUMBER(C63),ISNUMBER(D63),C63&lt;&gt;0),(C63-D63)/C63,"不可比")</f>
+        <v>-3.115975836948645</v>
+      </c>
+      <c r="F63" s="6">
+        <f>IF(AND(ISNUMBER(D63),54.50497163930999&lt;&gt;0),(54.50497163930999-D63)/54.50497163930999,"不可比")</f>
+        <v>0.13302045726120443</v>
+      </c>
+      <c r="G63" s="20">
+        <f>(37/100-1)*100</f>
+        <v>-63.0</v>
+      </c>
+      <c r="H63" s="20">
+        <f>(37/100-33/100)*100</f>
+        <v>3.9999999999999982</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="45" customHeight="1">
+      <c r="A64" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C64" s="7">
+        <v>11.4808</v>
+      </c>
+      <c r="D64" s="7">
+        <v>50.90068114483</v>
+      </c>
+      <c r="E64" s="6">
+        <f>IF(AND(ISNUMBER(C64),ISNUMBER(D64),C64&lt;&gt;0),(C64-D64)/C64,"不可比")</f>
+        <v>-3.433548284512403</v>
+      </c>
+      <c r="F64" s="6">
+        <f>IF(AND(ISNUMBER(D64),54.50497163930999&lt;&gt;0),(54.50497163930999-D64)/54.50497163930999,"不可比")</f>
+        <v>0.06612773818747425</v>
+      </c>
+      <c r="G64" s="20">
+        <f>(34/100-1)*100</f>
+        <v>-65.99999999999999</v>
+      </c>
+      <c r="H64" s="20">
+        <f>(34/100-33/100)*100</f>
+        <v>1.0000000000000009</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="45" customHeight="1">
+      <c r="A65" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C65" s="7">
+        <v>4.8756</v>
+      </c>
+      <c r="D65" s="7">
+        <v>5.376450884124</v>
+      </c>
+      <c r="E65" s="6">
+        <f>IF(AND(ISNUMBER(C65),ISNUMBER(D65),C65&lt;&gt;0),(C65-D65)/C65,"不可比")</f>
+        <v>-0.10272599969726795</v>
+      </c>
+      <c r="F65" s="6">
+        <f>IF(AND(ISNUMBER(D65),5.376450884124&lt;&gt;0),(5.376450884124-D65)/5.376450884124,"不可比")</f>
+        <v>0.0</v>
+      </c>
+      <c r="G65" s="20">
+        <f>(100/100-1)*100</f>
+        <v>0.0</v>
+      </c>
+      <c r="H65" s="20">
+        <f>(100/100-100/100)*100</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="45" customHeight="1">
+      <c r="A66" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66" s="7">
+        <v>4.8756</v>
+      </c>
+      <c r="D66" s="7">
+        <v>5.291779501674</v>
+      </c>
+      <c r="E66" s="6">
+        <f>IF(AND(ISNUMBER(C66),ISNUMBER(D66),C66&lt;&gt;0),(C66-D66)/C66,"不可比")</f>
+        <v>-0.08535964838666013</v>
+      </c>
+      <c r="F66" s="6">
+        <f>IF(AND(ISNUMBER(D66),5.376450884124&lt;&gt;0),(5.376450884124-D66)/5.376450884124,"不可比")</f>
+        <v>0.015748564299178053</v>
+      </c>
+      <c r="G66" s="20">
+        <f>(100/100-1)*100</f>
+        <v>0.0</v>
+      </c>
+      <c r="H66" s="20">
+        <f>(100/100-100/100)*100</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="45" customHeight="1">
+      <c r="A67" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C67" s="7">
+        <v>4.8756</v>
+      </c>
+      <c r="D67" s="7">
+        <v>4.993702343056</v>
+      </c>
+      <c r="E67" s="6">
+        <f>IF(AND(ISNUMBER(C67),ISNUMBER(D67),C67&lt;&gt;0),(C67-D67)/C67,"不可比")</f>
+        <v>-0.024223140342932166</v>
+      </c>
+      <c r="F67" s="6">
+        <f>IF(AND(ISNUMBER(D67),5.376450884124&lt;&gt;0),(5.376450884124-D67)/5.376450884124,"不可比")</f>
+        <v>0.07118981449234645</v>
+      </c>
+      <c r="G67" s="20">
+        <f>(100/100-1)*100</f>
+        <v>0.0</v>
+      </c>
+      <c r="H67" s="20">
+        <f>(100/100-100/100)*100</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="45" customHeight="1">
+      <c r="A68" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C68" s="7">
+        <v>4.8756</v>
+      </c>
+      <c r="D68" s="7">
+        <v>4.901756139286</v>
+      </c>
+      <c r="E68" s="6">
+        <f>IF(AND(ISNUMBER(C68),ISNUMBER(D68),C68&lt;&gt;0),(C68-D68)/C68,"不可比")</f>
+        <v>-0.005364701633850232</v>
+      </c>
+      <c r="F68" s="6">
+        <f>IF(AND(ISNUMBER(D68),5.376450884124&lt;&gt;0),(5.376450884124-D68)/5.376450884124,"不可比")</f>
+        <v>0.08829146867866212</v>
+      </c>
+      <c r="G68" s="20">
+        <f>(100/100-1)*100</f>
+        <v>0.0</v>
+      </c>
+      <c r="H68" s="20">
+        <f>(100/100-100/100)*100</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="45" customHeight="1">
+      <c r="A69" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C69" s="7">
+        <v>4.356</v>
+      </c>
+      <c r="D69" s="7">
+        <v>123.2346789297831</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="F69" s="6">
+        <f>IF(AND(ISNUMBER(D69),123.23467892978313&lt;&gt;0),(123.23467892978313-D69)/123.23467892978313,"不可比")</f>
+        <v>0.0</v>
+      </c>
+      <c r="G69" s="20">
+        <f>(76/100-1)*100</f>
+        <v>-24.0</v>
+      </c>
+      <c r="H69" s="20">
+        <f>(76/100-76/100)*100</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="45" customHeight="1">
+      <c r="A70" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70" s="7">
+        <v>4.356</v>
+      </c>
+      <c r="D70" s="7">
+        <v>123.2346789297831</v>
+      </c>
+      <c r="E70" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="F70" s="6">
+        <f>IF(AND(ISNUMBER(D70),123.23467892978313&lt;&gt;0),(123.23467892978313-D70)/123.23467892978313,"不可比")</f>
+        <v>0.0</v>
+      </c>
+      <c r="G70" s="20">
+        <f>(76/100-1)*100</f>
+        <v>-24.0</v>
+      </c>
+      <c r="H70" s="20">
+        <f>(76/100-76/100)*100</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="45" customHeight="1">
+      <c r="A71" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C71" s="7">
+        <v>4.356</v>
+      </c>
+      <c r="D71" s="7">
+        <v>299.4917599032963</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="G71" s="20">
+        <f>(69/100-1)*100</f>
+        <v>-31.000000000000007</v>
+      </c>
+      <c r="H71" s="20">
+        <f>(69/100-76/100)*100</f>
+        <v>-7.000000000000006</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" ht="45" customHeight="1">
+      <c r="A72" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C72" s="7">
+        <v>4.356</v>
+      </c>
+      <c r="D72" s="7">
+        <v>252.1680517323086</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="G72" s="20">
+        <f>(70/100-1)*100</f>
+        <v>-30.000000000000004</v>
+      </c>
+      <c r="H72" s="20">
+        <f>(70/100-76/100)*100</f>
+        <v>-6.000000000000005</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="45" customHeight="1">
+      <c r="A73" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C73" s="7">
+        <v>15.3427</v>
+      </c>
+      <c r="D73" s="7">
+        <v>12.62093021071654</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="F73" s="6">
+        <f>IF(AND(ISNUMBER(D73),12.620930210716535&lt;&gt;0),(12.620930210716535-D73)/12.620930210716535,"不可比")</f>
+        <v>0.0</v>
+      </c>
+      <c r="G73" s="20">
+        <f>(114/150-1)*100</f>
+        <v>-24.0</v>
+      </c>
+      <c r="H73" s="20">
+        <f>(114/150-114/150)*100</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="45" customHeight="1">
+      <c r="A74" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C74" s="7">
+        <v>15.3427</v>
+      </c>
+      <c r="D74" s="7">
+        <v>10.97050868271654</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="F74" s="6">
+        <f>IF(AND(ISNUMBER(D74),12.620930210716535&lt;&gt;0),(12.620930210716535-D74)/12.620930210716535,"不可比")</f>
+        <v>0.13076861217397537</v>
+      </c>
+      <c r="G74" s="20">
+        <f>(121/150-1)*100</f>
+        <v>-19.333333333333336</v>
+      </c>
+      <c r="H74" s="20">
+        <f>(121/150-114/150)*100</f>
+        <v>4.666666666666663</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" ht="45" customHeight="1">
+      <c r="A75" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C75" s="7">
+        <v>15.3427</v>
+      </c>
+      <c r="D75" s="7">
+        <v>10.72940896452414</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="G75" s="20">
+        <f>(138/150-1)*100</f>
+        <v>-7.9999999999999964</v>
+      </c>
+      <c r="H75" s="20">
+        <f>(138/150-114/150)*100</f>
+        <v>16.000000000000004</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="45" customHeight="1">
+      <c r="A76" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C76" s="7">
+        <v>15.3427</v>
+      </c>
+      <c r="D76" s="7">
+        <v>9.095719413689656</v>
+      </c>
+      <c r="E76" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="G76" s="20">
+        <f>(144/150-1)*100</f>
+        <v>-4.0000000000000036</v>
+      </c>
+      <c r="H76" s="20">
+        <f>(144/150-114/150)*100</f>
+        <v>19.999999999999996</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" ht="66" customHeight="1">
+      <c r="A79" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="2"/>
+      <c r="E79" s="2"/>
+      <c r="F79" s="2"/>
+      <c r="G79" s="2"/>
+      <c r="H79" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="8">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="A29:H29"/>
     <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A55:H55"/>
+    <mergeCell ref="A79:H79"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.4" bottom="0.4" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" fitToHeight="0" orientation="landscape"/>
